--- a/excel/d-l-f-medina-rivera-s-a_capacitaciones.xlsx
+++ b/excel/d-l-f-medina-rivera-s-a_capacitaciones.xlsx
@@ -1592,12 +1592,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C001748448</t>
+          <t>C001754078</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C001748448 - ATANACIO GOMERO LIDIA BRIGITTE</t>
+          <t>C001754078 - VASQUEZ BELLIDO HAUSEMAN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C001748948</t>
+          <t>C001748448</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C001748948 - MAURICIO AYALA GIOVANNA MARGARITA</t>
+          <t>C001748448 - ATANACIO GOMERO LIDIA BRIGITTE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C004043481</t>
+          <t>C001748948</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C004043481 - YHA FERNANDEZ JUAN MANUEL</t>
+          <t>C001748948 - MAURICIO AYALA GIOVANNA MARGARITA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1806,9 +1806,21 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
@@ -1850,12 +1862,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C004043607</t>
+          <t>C004094955</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C004043607 - FLORES LEON MARISELLA DEL CARMEN</t>
+          <t>C004094955 - MIRANDA PEDROSO YESSENIA FLOR</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1886,12 +1898,12 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1902,17 +1914,13 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1952,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C001754078</t>
+          <t>C004044635</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C001754078 - VASQUEZ BELLIDO HAUSEMAN</t>
+          <t>C004044635 - MOREYRA JACOBO MARTIN JESUS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2024,7 +2032,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No le interesa aprender la app</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2034,12 +2042,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C001765944</t>
+          <t>C004043481</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C001765944 - DUEÑAS LLUCHO SEGUNDO PEDRO</t>
+          <t>C004043481 - YHA FERNANDEZ JUAN MANUEL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2112,12 +2120,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C004094955</t>
+          <t>C004043607</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C004094955 - MIRANDA PEDROSO YESSENIA FLOR</t>
+          <t>C004043607 - FLORES LEON MARISELLA DEL CARMEN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2148,12 +2156,12 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2164,13 +2172,17 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2204,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No le interesa aprender la app</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2202,17 +2214,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C004044635</t>
+          <t>C001765944</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C004044635 - MOREYRA JACOBO MARTIN JESUS</t>
+          <t>C001765944 - DUEÑAS LLUCHO SEGUNDO PEDRO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -2225,7 +2237,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2236,21 +2248,9 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
@@ -2808,12 +2808,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C001326551</t>
+          <t>C004159019</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C001326551 - VALDEZ ARQUINEGO JOSE</t>
+          <t>C004159019 - BRAVO DIAZ LUZ LEANDRA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001291938</t>
+          <t>C004181103</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C001291938 - MERINO MONZON SANTOS</t>
+          <t>C004181103 - VARGAS PEREIRA GUILLERMO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C001504119</t>
+          <t>C004180272</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C001504119 - SINFOROSO ALEGRIA DE SILVERA NELLY LUZ</t>
+          <t>C004180272 - ANDIA FAUCHEUX YRIS MARIELLA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3024,12 +3024,12 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C001480676</t>
+          <t>C001766067</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C001480676 - YARANGA MARTIN SANDY GLADIS</t>
+          <t>C001766067 - CHAMORRO BENDEZU PABLINA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C001481150</t>
+          <t>C001759441</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C001481150 - GUERRA GUTIERREZ DENY RUTH</t>
+          <t>C001759441 - GONZALES MAGUINA CINZIA GIULIANA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3204,7 +3204,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C001654069</t>
+          <t>C001759461</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C001654069 - CAPUÑAY CORNEJO ANTHONY JAMPIERE</t>
+          <t>C001759461 - LUQUE YANCUNTA CRISTINA ELIZABETH</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3348,17 +3348,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C001722681</t>
+          <t>C001759673</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C001722681 - LOYOLA LUNA MARIBEL</t>
+          <t>C001759673 - NAVARRO FUENTES ISABEL HONORIA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3379,28 +3379,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Poco dispuesto</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
@@ -3442,12 +3426,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C001766067</t>
+          <t>C001762297</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C001766067 - CHAMORRO BENDEZU PABLINA</t>
+          <t>C001762297 - SANCHEZ CASTILLO JENRRY RONALD</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3483,7 +3467,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3532,12 +3516,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C001759441</t>
+          <t>C001722681</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C001759441 - GONZALES MAGUINA CINZIA GIULIANA</t>
+          <t>C001722681 - LOYOLA LUNA MARIBEL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3563,17 +3547,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3622,12 +3610,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C001759461</t>
+          <t>C001326551</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C001759461 - LUQUE YANCUNTA CRISTINA ELIZABETH</t>
+          <t>C001326551 - VALDEZ ARQUINEGO JOSE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3702,7 +3690,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3712,17 +3700,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C001759673</t>
+          <t>C001291938</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C001759673 - NAVARRO FUENTES ISABEL HONORIA</t>
+          <t>C001291938 - MERINO MONZON SANTOS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
@@ -3735,7 +3723,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3746,9 +3734,21 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C001762297</t>
+          <t>C001504119</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C001762297 - SANCHEZ CASTILLO JENRRY RONALD</t>
+          <t>C001504119 - SINFOROSO ALEGRIA DE SILVERA NELLY LUZ</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3826,7 +3826,7 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C004159019</t>
+          <t>C001480676</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C004159019 - BRAVO DIAZ LUZ LEANDRA</t>
+          <t>C001480676 - YARANGA MARTIN SANDY GLADIS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C004181103</t>
+          <t>C001481150</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C004181103 - VARGAS PEREIRA GUILLERMO</t>
+          <t>C001481150 - GUERRA GUTIERREZ DENY RUTH</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4006,7 +4006,7 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C004180272</t>
+          <t>C001654069</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C004180272 - ANDIA FAUCHEUX YRIS MARIELLA</t>
+          <t>C001654069 - CAPUÑAY CORNEJO ANTHONY JAMPIERE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C004241978</t>
+          <t>C004034148</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C004241978 - DETALLES STORE EVENTOS Y DECORACIONES S.</t>
+          <t>C004034148 - CHIPANA SALCEDO ANGELICA HILDA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4588,12 +4588,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C001563636</t>
+          <t>C001572036</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C001563636 - MENDOZA BACCA ETELVINA JESUS</t>
+          <t>C001572036 - CHOMBO ORTIZ JESSICA FERNANDA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C001402353</t>
+          <t>C001617965</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C001402353 - BARRETO ROJAS JOSE LUIS</t>
+          <t>C001617965 - RAVELLO NEGRON MAXIMILIANO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
@@ -4768,12 +4768,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C004142651</t>
+          <t>C001713132</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C004142651 - COSAR CAPARACHIN ESPIRITA BERTHA</t>
+          <t>C001713132 - JULCA FABIAN RONAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C004034148</t>
+          <t>C001717695</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C004034148 - CHIPANA SALCEDO ANGELICA HILDA</t>
+          <t>C001717695 - MILLONES LOPEZ MARIA JESUS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Persona no tecnológica / tercera edad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4948,17 +4948,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C004051473</t>
+          <t>C001718083</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C004051473 - RAMOS MAMANI BENEDICTO</t>
+          <t>C001718083 - RAMOS SALDARRIAGA SARITA MILAGROS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4982,21 +4982,9 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
@@ -5038,12 +5026,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C004187958</t>
+          <t>C001743137</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C004187958 - JULCA CASTILLO MARTIN SANTOS</t>
+          <t>C001743137 - MGD ASESORES Y CONSULTORES S.A.C.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5128,12 +5116,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C001743137</t>
+          <t>C004142651</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C001743137 - MGD ASESORES Y CONSULTORES S.A.C.</t>
+          <t>C004142651 - COSAR CAPARACHIN ESPIRITA BERTHA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5208,7 +5196,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Persona no tecnológica / tercera edad</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5218,17 +5206,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C001718083</t>
+          <t>C004165733</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C001718083 - RAMOS SALDARRIAGA SARITA MILAGROS</t>
+          <t>C004165733 - FERNANDEZ VASQUEZ ANGEL GABRIEL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
@@ -5241,7 +5229,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5252,9 +5240,21 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C001474177</t>
+          <t>C004051473</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C001474177 - QUISPE HUAMAN JOSE LUIS</t>
+          <t>C004051473 - RAMOS MAMANI BENEDICTO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C001572036</t>
+          <t>C004187958</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C001572036 - CHOMBO ORTIZ JESSICA FERNANDA</t>
+          <t>C004187958 - JULCA CASTILLO MARTIN SANTOS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C001554354</t>
+          <t>C004241978</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C001554354 - PANDURO CRUZ SANDRA LUZ</t>
+          <t>C004241978 - DETALLES STORE EVENTOS Y DECORACIONES S.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C001717695</t>
+          <t>C004237004</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C001717695 - MILLONES LOPEZ MARIA JESUS</t>
+          <t>C004237004 - CHAVEZ SALAS VALERIANA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C001713132</t>
+          <t>C004203631</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C001713132 - JULCA FABIAN RONAL</t>
+          <t>C004203631 - ARANDA RODRIGUEZ HENRY JULIO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C001617965</t>
+          <t>C001554354</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C001617965 - RAVELLO NEGRON MAXIMILIANO</t>
+          <t>C001554354 - PANDURO CRUZ SANDRA LUZ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Más capacitación</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
@@ -5836,12 +5836,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C004237004</t>
+          <t>C001563636</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C004237004 - CHAVEZ SALAS VALERIANA</t>
+          <t>C001563636 - MENDOZA BACCA ETELVINA JESUS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C004203631</t>
+          <t>C001474177</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C004203631 - ARANDA RODRIGUEZ HENRY JULIO</t>
+          <t>C001474177 - QUISPE HUAMAN JOSE LUIS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C004165733</t>
+          <t>C001402353</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C004165733 - FERNANDEZ VASQUEZ ANGEL GABRIEL</t>
+          <t>C001402353 - BARRETO ROJAS JOSE LUIS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6106,12 +6106,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C001715124</t>
+          <t>C001766040</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C001715124 - MURRIETA SANDOVAL DEYANIRA VENUS MILAGRO</t>
+          <t>C001766040 - ALBUJAR RAMIREZ ERIKA LUCIA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C001568676</t>
+          <t>C004049602</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C001568676 - CHIPURGO TORRES MILAGROS MARITZA</t>
+          <t>C004049602 - CALLIRGOS RODRIGUEZ INES</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C001402765</t>
+          <t>C004039089</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C001402765 - QUICAÑO DE CCANTO JULIA</t>
+          <t>C004039089 - SAAVEDRA LUCANO SEGUNDO CESAR</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C000232226</t>
+          <t>C004096441</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C000232226 - BAZAN BEDON ROSA</t>
+          <t>C004096441 - ELEJALDE GUZMAN CARMEN ARIELA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C001766040</t>
+          <t>C004242751</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>C001766040 - ALBUJAR RAMIREZ ERIKA LUCIA</t>
+          <t>C004242751 - RIOS MAURICIO ARMINDA GABRIELA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C004096441</t>
+          <t>C004239739</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C004096441 - ELEJALDE GUZMAN CARMEN ARIELA</t>
+          <t>C004239739 - PEÑA QUISPE POL NELSON</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C004049602</t>
+          <t>C000232226</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C004049602 - CALLIRGOS RODRIGUEZ INES</t>
+          <t>C000232226 - BAZAN BEDON ROSA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C001740024</t>
+          <t>C001402765</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C001740024 - MORAN VACA BETTY AURORA</t>
+          <t>C001402765 - QUICAÑO DE CCANTO JULIA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6916,12 +6916,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C004242751</t>
+          <t>C001740024</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C004242751 - RIOS MAURICIO ARMINDA GABRIELA</t>
+          <t>C001740024 - MORAN VACA BETTY AURORA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C001763295</t>
+          <t>C004242752</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C001763295 - MACHUCA MARQUEZ MILAGROS MERCEDES</t>
+          <t>C004242752 - TORRES SHIMIZU SHARON AKEMI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C004239739</t>
+          <t>C004216600</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C004239739 - PEÑA QUISPE POL NELSON</t>
+          <t>C004216600 - MEZA GARAY YESSICA JACQUELINE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C004039089</t>
+          <t>C001763295</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C004039089 - SAAVEDRA LUCANO SEGUNDO CESAR</t>
+          <t>C001763295 - MACHUCA MARQUEZ MILAGROS MERCEDES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C004242752</t>
+          <t>C001715124</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C004242752 - TORRES SHIMIZU SHARON AKEMI</t>
+          <t>C001715124 - MURRIETA SANDOVAL DEYANIRA VENUS MILAGRO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C004216600</t>
+          <t>C001568676</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C004216600 - MEZA GARAY YESSICA JACQUELINE</t>
+          <t>C001568676 - CHIPURGO TORRES MILAGROS MARITZA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10396,17 +10396,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>C004176857</t>
+          <t>C004190738</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>C004176857 - SILVA NUÑEZ MARIA LUZVINDA</t>
+          <t>C004190738 - GUTIERREZ SAEZ ANTONINA OLIMPIA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10430,21 +10430,9 @@
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>Confirmar pedido</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr">
         <is>
@@ -10486,12 +10474,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>C004178077</t>
+          <t>C001759391</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>C004178077 - JIMENEZ GUERRERO MARIA</t>
+          <t>C001759391 - AVALOS GAVILAN DE PATRICIO JACKELINE</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10527,7 +10515,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10576,12 +10564,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>C001104266</t>
+          <t>C004176857</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>C001104266 - BALLENA CUSTODIO TITO MIGUEL</t>
+          <t>C004176857 - SILVA NUÑEZ MARIA LUZVINDA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10617,7 +10605,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10656,7 +10644,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10666,17 +10654,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>C000234453</t>
+          <t>C004178077</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>C000234453 - TORRES QUISPE SEGUNDINA</t>
+          <t>C004178077 - JIMENEZ GUERRERO MARIA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
@@ -10689,7 +10677,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -10700,9 +10688,21 @@
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr">
         <is>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C001565116</t>
+          <t>C001104266</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>C001565116 - SOLAR CAMPOS LEANDRO MERINO</t>
+          <t>C001104266 - BALLENA CUSTODIO TITO MIGUEL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C004190738</t>
+          <t>C000234453</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>C004190738 - GUTIERREZ SAEZ ANTONINA OLIMPIA</t>
+          <t>C000234453 - TORRES QUISPE SEGUNDINA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -10912,12 +10912,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>C001759391</t>
+          <t>C001565116</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>C001759391 - AVALOS GAVILAN DE PATRICIO JACKELINE</t>
+          <t>C001565116 - SOLAR CAMPOS LEANDRO MERINO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>C000233740</t>
+          <t>C001087818</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>C000233740 - REYES CANCHIS MELISSA</t>
+          <t>C001087818 - BARZOLA CUADRADO LUZMILA ZORAIDA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -11182,12 +11182,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>C000237343</t>
+          <t>C000233740</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>C000237343 - SOSA JUAREZ DE MARCHENA BENITA SIMONA</t>
+          <t>C000233740 - REYES CANCHIS MELISSA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>C001087818</t>
+          <t>C000237343</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>C001087818 - BARZOLA CUADRADO LUZMILA ZORAIDA</t>
+          <t>C000237343 - SOSA JUAREZ DE MARCHENA BENITA SIMONA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>C001326934</t>
+          <t>C001360767</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>C001326934 - SOLAR CAMPOS JUAN CARLOS</t>
+          <t>C001360767 - CORPORACION MERCANTIL DECAR S.A.C.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -11414,13 +11414,17 @@
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Vendedor</t>
+        </is>
+      </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Vendedor hizo pedido (no autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11452,12 +11456,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C001360767</t>
+          <t>C001364446</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>C001360767 - CORPORACION MERCANTIL DECAR S.A.C.</t>
+          <t>C001364446 - DOMINGUEZ LOPEZ MARTIN ENRIQUE</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11493,7 +11497,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -11504,17 +11508,13 @@
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>Vendedor</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr">
         <is>
-          <t>SI - Vendedor hizo pedido (no autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -11546,12 +11546,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>C001364446</t>
+          <t>C001326934</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>C001364446 - DOMINGUEZ LOPEZ MARTIN ENRIQUE</t>
+          <t>C001326934 - SOLAR CAMPOS JUAN CARLOS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -11636,17 +11636,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>C001368673</t>
+          <t>C001405660</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>C001368673 - DE LA CRUZ CAHUANA DANTE</t>
+          <t>C001405660 - MENDOZA TARAZONA ROSARIO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -11670,21 +11670,9 @@
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr">
         <is>
@@ -11716,7 +11704,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -11726,17 +11714,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C001405660</t>
+          <t>C001368673</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>C001405660 - MENDOZA TARAZONA ROSARIO</t>
+          <t>C001368673 - DE LA CRUZ CAHUANA DANTE</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
@@ -11749,7 +11737,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -11760,9 +11748,21 @@
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr">
         <is>
@@ -11804,12 +11804,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C001678688</t>
+          <t>C001629322</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>C001678688 - SOTELO NAVARRO FREDY ALFREDO</t>
+          <t>C001629322 - CERNA MEGO NELLY NAYDA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>C001629322</t>
+          <t>C001678688</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>C001629322 - CERNA MEGO NELLY NAYDA</t>
+          <t>C001678688 - SOTELO NAVARRO FREDY ALFREDO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -12074,12 +12074,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>C004037245</t>
+          <t>C004159601</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>C004037245 - FLORIAN DIAZ CLARA FANY</t>
+          <t>C004159601 - BALLENA FLORES CINDY ROCIO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -12105,11 +12105,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
@@ -12119,7 +12115,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -12258,12 +12254,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>C004159601</t>
+          <t>C004037245</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>C004159601 - BALLENA FLORES CINDY ROCIO</t>
+          <t>C004037245 - FLORIAN DIAZ CLARA FANY</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -12289,7 +12285,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>C001579394</t>
+          <t>C001519536</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>C001579394 - INVERSIONES MARCELO VILLANUEVA MV E.I.R.</t>
+          <t>C001519536 - ACUÑA GAMARRA MARIO RONEL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>C001617106</t>
+          <t>C001579394</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>C001617106 - AVILA MALDONADO JOVITA GLADYS</t>
+          <t>C001579394 - INVERSIONES MARCELO VILLANUEVA MV E.I.R.</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>C001519536</t>
+          <t>C001617106</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>C001519536 - ACUÑA GAMARRA MARIO RONEL</t>
+          <t>C001617106 - AVILA MALDONADO JOVITA GLADYS</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -15094,12 +15094,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>C001576586</t>
+          <t>C001658239</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>C001576586 - MADERO ALAYO ELIZABETH MARIA</t>
+          <t>C001658239 - GOMEZ ENRIQUEZ LUZ VIOLETA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -15188,17 +15188,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>C001569164</t>
+          <t>C001576586</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>C001569164 - CHAMAYA MARQUEZ REYNERIO</t>
+          <t>C001576586 - MADERO ALAYO ELIZABETH MARIA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -15222,9 +15222,21 @@
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
-      <c r="R167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr">
         <is>
@@ -15260,7 +15272,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -15270,17 +15282,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>C001573340</t>
+          <t>C001569164</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>C001573340 - CASTILLO CORDOVA ELIAS</t>
+          <t>C001569164 - CHAMAYA MARQUEZ REYNERIO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
@@ -15293,7 +15305,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -15304,21 +15316,9 @@
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R168" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr">
         <is>
@@ -15327,12 +15327,12 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V168" t="inlineStr">
         <is>
-          <t>SI - Vendedor hizo pedido (no autogestionado)</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -15364,17 +15364,17 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>C001550829</t>
+          <t>C001573340</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>C001550829 - SIFUENTES DIAZ MAGDA MAGDALENA</t>
+          <t>C001573340 - CASTILLO CORDOVA ELIAS</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -15398,19 +15398,35 @@
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U169" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Vendedor</t>
+        </is>
+      </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Vendedor hizo pedido (no autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15432,7 +15448,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15442,17 +15458,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>C001683341</t>
+          <t>C001550829</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>C001683341 - CRUZ LUCIANA</t>
+          <t>C001550829 - SIFUENTES DIAZ MAGDA MAGDALENA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
@@ -15465,7 +15481,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -15476,35 +15492,19 @@
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
       <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -15536,12 +15536,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>C001728940</t>
+          <t>C001683341</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>C001728940 - RAMOS RAMIREZ ALEJANDRO</t>
+          <t>C001683341 - CRUZ LUCIANA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -15593,12 +15593,12 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15630,12 +15630,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>C001658239</t>
+          <t>C001728940</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>C001658239 - GOMEZ ENRIQUEZ LUZ VIOLETA</t>
+          <t>C001728940 - RAMOS RAMIREZ ALEJANDRO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -15687,12 +15687,12 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -15724,12 +15724,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>C004039136</t>
+          <t>C001739677</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>C004039136 - RODRIGUEZ GONZALES CARLOS JESUS</t>
+          <t>C001739677 - OYOLA OYOLA FIORELLA NATALY</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15776,17 +15776,13 @@
       <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -15808,7 +15804,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15818,17 +15814,17 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>C004024351</t>
+          <t>C001745477</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>C004024351 - ROJAS TIRADO ROBIN LENIN</t>
+          <t>C001745477 - VEGA PEREDA CHABUCA MAVILA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I174" s="2" t="n">
@@ -15841,7 +15837,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -15852,35 +15848,19 @@
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
       <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -16358,12 +16338,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>C001739677</t>
+          <t>C004024351</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>C001739677 - OYOLA OYOLA FIORELLA NATALY</t>
+          <t>C004024351 - ROJAS TIRADO ROBIN LENIN</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -16410,13 +16390,17 @@
       <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U180" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V180" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16422,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -16448,17 +16432,17 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>C001745477</t>
+          <t>C004039136</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>C001745477 - VEGA PEREDA CHABUCA MAVILA</t>
+          <t>C004039136 - RODRIGUEZ GONZALES CARLOS JESUS</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I181" s="2" t="n">
@@ -16471,7 +16455,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -16482,19 +16466,35 @@
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
-      <c r="R181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S181" t="inlineStr"/>
       <c r="T181" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -17856,12 +17856,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>C001562933</t>
+          <t>C001537771</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>C001562933 - MEDINA ALTAMIRANO ELIAN CARLOS MALHER</t>
+          <t>C001537771 - INGA CERRON FELICITA VICTORIA</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -17908,17 +17908,13 @@
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -17950,12 +17946,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>C001537771</t>
+          <t>C001562933</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>C001537771 - INGA CERRON FELICITA VICTORIA</t>
+          <t>C001562933 - MEDINA ALTAMIRANO ELIAN CARLOS MALHER</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -18002,13 +17998,17 @@
       <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V198" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Persona no tecnológica / tercera edad</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -18134,17 +18134,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>C001630592</t>
+          <t>C001664822</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>C001630592 - ESPINOZA ALMINAGORDA EVA</t>
+          <t>C001664822 - RISCO VEGA FELICITAS</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I200" s="2" t="n">
@@ -18157,7 +18157,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -18168,21 +18168,9 @@
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R200" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
       <c r="S200" t="inlineStr"/>
       <c r="T200" t="inlineStr">
         <is>
@@ -18214,7 +18202,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Persona no tecnológica / tercera edad</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -18224,17 +18212,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>C001664822</t>
+          <t>C001630592</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>C001664822 - RISCO VEGA FELICITAS</t>
+          <t>C001630592 - ESPINOZA ALMINAGORDA EVA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I201" s="2" t="n">
@@ -18247,7 +18235,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -18258,9 +18246,21 @@
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
-      <c r="R201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S201" t="inlineStr"/>
       <c r="T201" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -18302,17 +18302,17 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>C001723315</t>
+          <t>C001722364</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>C001723315 - VERA ZAPATA YULIMER</t>
+          <t>C001722364 - VILLANUEVA VARGAS MARISA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I202" s="2" t="n">
@@ -18325,7 +18325,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -18336,9 +18336,21 @@
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
-      <c r="R202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Ver promociones</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr">
         <is>
@@ -18370,7 +18382,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -18380,17 +18392,17 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>C001724853</t>
+          <t>C001723315</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>C001724853 - CUMPA GONZALES YRIS</t>
+          <t>C001723315 - VERA ZAPATA YULIMER</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I203" s="2" t="n">
@@ -18403,7 +18415,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -18414,35 +18426,19 @@
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R203" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr"/>
       <c r="T203" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -18464,7 +18460,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -18474,17 +18470,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>C001748740</t>
+          <t>C001724853</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>C001748740 - PALACIOS FARFAN YSABEL</t>
+          <t>C001724853 - CUMPA GONZALES YRIS</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I204" s="2" t="n">
@@ -18497,7 +18493,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -18508,9 +18504,21 @@
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr"/>
-      <c r="R204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S204" t="inlineStr"/>
       <c r="T204" t="inlineStr">
         <is>
@@ -18519,12 +18527,12 @@
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18546,7 +18554,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -18556,17 +18564,17 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>C001754511</t>
+          <t>C001734390</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>C001754511 - REYES HERNANDEZ JESUS OSWALDO</t>
+          <t>C001734390 - TARAZONA FIGUEROA ERIKA LUZ</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I205" s="2" t="n">
@@ -18579,7 +18587,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -18590,19 +18598,35 @@
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
-      <c r="R205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U205" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V205" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18648,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -18634,17 +18658,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>C001734390</t>
+          <t>C001748740</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>C001734390 - TARAZONA FIGUEROA ERIKA LUZ</t>
+          <t>C001748740 - PALACIOS FARFAN YSABEL</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I206" s="2" t="n">
@@ -18657,7 +18681,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -18668,21 +18692,9 @@
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr">
         <is>
@@ -18691,12 +18703,12 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -18718,7 +18730,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -18728,17 +18740,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>C001722364</t>
+          <t>C001754511</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>C001722364 - VILLANUEVA VARGAS MARISA</t>
+          <t>C001754511 - REYES HERNANDEZ JESUS OSWALDO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I207" s="2" t="n">
@@ -18751,7 +18763,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -18762,21 +18774,9 @@
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>Ver promociones</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -18998,17 +18998,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>C004095424</t>
+          <t>C004036738</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>C004095424 - YAPAN KAYPI S.A.C.</t>
+          <t>C004036738 - URBANO SALINAS DE TOMAS MARIVEL ROSARIO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I210" s="2" t="n">
@@ -19021,7 +19021,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -19032,21 +19032,9 @@
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R210" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr">
         <is>
@@ -19088,12 +19076,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>C004098431</t>
+          <t>C004095424</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>C004098431 - GARCIA LOPEZ JEAN CARLOS</t>
+          <t>C004095424 - YAPAN KAYPI S.A.C.</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -19129,7 +19117,7 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -19168,7 +19156,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -19178,17 +19166,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C004036738</t>
+          <t>C004098431</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>C004036738 - URBANO SALINAS DE TOMAS MARIVEL ROSARIO</t>
+          <t>C004098431 - GARCIA LOPEZ JEAN CARLOS</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I212" s="2" t="n">
@@ -19201,7 +19189,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -19212,9 +19200,21 @@
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
-      <c r="R212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr">
         <is>
@@ -19956,12 +19956,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>C001524222</t>
+          <t>C001556735</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>C001524222 - CUYA CISNEROS TERESA</t>
+          <t>C001556735 - CORDOVA CESPEDES DEYANIRA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -19992,33 +19992,29 @@
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr"/>
       <c r="V221" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -20050,12 +20046,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>C001556735</t>
+          <t>C001524222</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>C001556735 - CORDOVA CESPEDES DEYANIRA</t>
+          <t>C001524222 - CUYA CISNEROS TERESA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -20086,29 +20082,33 @@
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U222" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V222" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -20140,17 +20140,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>C001573709</t>
+          <t>C001653855</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>C001573709 - MALLQUI PINILLOS SARA CLAUDINA</t>
+          <t>C001653855 - LIPE FLORES SERGIO FREDY</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I223" s="2" t="n">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -20174,23 +20174,31 @@
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
-      <c r="R223" t="inlineStr"/>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -20212,7 +20220,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -20222,17 +20230,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>C001653855</t>
+          <t>C001573709</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>C001653855 - LIPE FLORES SERGIO FREDY</t>
+          <t>C001573709 - MALLQUI PINILLOS SARA CLAUDINA</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I224" s="2" t="n">
@@ -20245,7 +20253,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -20256,31 +20264,23 @@
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>Confirmar pedido</t>
-        </is>
-      </c>
-      <c r="R224" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -20500,12 +20500,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>C001765713</t>
+          <t>C001759170</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>C001765713 - ROMAN ROSALES JOSE LUIS</t>
+          <t>C001759170 - VARGAS ZAMUDIO JUANA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -20536,12 +20536,12 @@
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
@@ -20594,12 +20594,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>C001759170</t>
+          <t>C001765713</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>C001759170 - VARGAS ZAMUDIO JUANA</t>
+          <t>C001765713 - ROMAN ROSALES JOSE LUIS</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -20630,12 +20630,12 @@
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Persona no tecnológica / tercera edad</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -20688,17 +20688,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>C004180522</t>
+          <t>C004168922</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>C004180522 - MANDRUNI VELA SANDRA</t>
+          <t>C004168922 - RIOS SANCHEZ ROSARIO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I229" s="2" t="n">
@@ -20711,7 +20711,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -20722,21 +20722,9 @@
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q229" t="inlineStr">
-        <is>
-          <t>Confirmar pedido</t>
-        </is>
-      </c>
-      <c r="R229" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr"/>
       <c r="T229" t="inlineStr">
         <is>
@@ -20768,7 +20756,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Persona no tecnológica / tercera edad</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -20778,17 +20766,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>C004044392</t>
+          <t>C004180522</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>C004044392 - FLORES APAZA CARMENA</t>
+          <t>C004180522 - MANDRUNI VELA SANDRA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I230" s="2" t="n">
@@ -20801,7 +20789,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -20812,9 +20800,21 @@
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
-      <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr"/>
-      <c r="R230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S230" t="inlineStr"/>
       <c r="T230" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Persona no tecnológica / tercera edad</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -20856,17 +20856,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>C004174512</t>
+          <t>C004044392</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>C004174512 - REQUEJO CALDERON EDWAR YOBERT</t>
+          <t>C004044392 - FLORES APAZA CARMENA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I231" s="2" t="n">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -20890,35 +20890,19 @@
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>Confirmar pedido</t>
-        </is>
-      </c>
-      <c r="R231" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr"/>
       <c r="V231" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -20940,7 +20924,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Persona no tecnológica / tercera edad</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -20950,17 +20934,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>C004168922</t>
+          <t>C004174512</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>C004168922 - RIOS SANCHEZ ROSARIO</t>
+          <t>C004174512 - REQUEJO CALDERON EDWAR YOBERT</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I232" s="2" t="n">
@@ -20973,7 +20957,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -20984,19 +20968,35 @@
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
-      <c r="R232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S232" t="inlineStr"/>
       <c r="T232" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U232" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V232" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21488,7 +21488,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>Tuvo una mala experiencia previa usando Diadía</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -21498,12 +21498,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>C001678803</t>
+          <t>C001693184</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>C001678803 - SULCA HUACAUSE LUISA FLOR</t>
+          <t>C001693184 - CALVAY CALVAY NATIVA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -21543,12 +21543,12 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V238" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -21570,7 +21570,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Tuvo una mala experiencia previa usando Diadía</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -21580,12 +21580,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>C001693184</t>
+          <t>C001678803</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>C001693184 - CALVAY CALVAY NATIVA</t>
+          <t>C001678803 - SULCA HUACAUSE LUISA FLOR</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -21625,12 +21625,12 @@
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -23402,7 +23402,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -23412,17 +23412,17 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>C001424838</t>
+          <t>C001577593</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>C001424838 - HUANCA LUQUE MARIA ELENA</t>
+          <t>C001577593 - MESCUA CORDOVA NANCY</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I259" s="2" t="n">
@@ -23435,7 +23435,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -23446,9 +23446,21 @@
       <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
-      <c r="P259" t="inlineStr"/>
-      <c r="Q259" t="inlineStr"/>
-      <c r="R259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S259" t="inlineStr"/>
       <c r="T259" t="inlineStr">
         <is>
@@ -23484,7 +23496,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -23494,17 +23506,17 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>C001664870</t>
+          <t>C001424838</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>C001664870 - SANTAMARIA SANDOVAL JULISSA</t>
+          <t>C001424838 - HUANCA LUQUE MARIA ELENA</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I260" s="2" t="n">
@@ -23517,7 +23529,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -23528,31 +23540,23 @@
       <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr"/>
-      <c r="P260" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q260" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R260" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr"/>
       <c r="S260" t="inlineStr"/>
       <c r="T260" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U260" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V260" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -23584,12 +23588,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>C001577593</t>
+          <t>C001664870</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>C001577593 - MESCUA CORDOVA NANCY</t>
+          <t>C001664870 - SANTAMARIA SANDOVAL JULISSA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -23625,7 +23629,7 @@
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -23636,17 +23640,13 @@
       <c r="S261" t="inlineStr"/>
       <c r="T261" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr"/>
       <c r="V261" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -23762,7 +23762,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -23772,17 +23772,17 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>C001679254</t>
+          <t>C001660450</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>C001679254 - LUQUE HUAMAN JAVIER REYNALDO</t>
+          <t>C001660450 - OROCOLLO CUEVA MARIO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I263" s="2" t="n">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -23806,31 +23806,23 @@
       <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr"/>
-      <c r="P263" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q263" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R263" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr"/>
       <c r="S263" t="inlineStr"/>
       <c r="T263" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U263" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -23862,12 +23854,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>C001734829</t>
+          <t>C001662599</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>C001734829 - MACHACA ORTIZ EDITH MARY</t>
+          <t>C001662599 - ZAPATA AGUILAR MERCEDES</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -23903,7 +23895,7 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -23956,12 +23948,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>C001517901</t>
+          <t>C001679254</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>C001517901 - AÑANCA QUISPE OSCAR</t>
+          <t>C001679254 - LUQUE HUAMAN JAVIER REYNALDO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -24008,17 +24000,13 @@
       <c r="S265" t="inlineStr"/>
       <c r="T265" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr"/>
       <c r="V265" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -24040,7 +24028,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -24050,17 +24038,17 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>C001465182</t>
+          <t>C001734829</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>C001465182 - LEFONCIO SANCHEZ CRISTIAN ALEXIS</t>
+          <t>C001734829 - MACHACA ORTIZ EDITH MARY</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I266" s="2" t="n">
@@ -24073,7 +24061,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -24084,9 +24072,21 @@
       <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
-      <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="inlineStr"/>
-      <c r="R266" t="inlineStr"/>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S266" t="inlineStr"/>
       <c r="T266" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -24308,17 +24308,17 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>C001660450</t>
+          <t>C001517901</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>C001660450 - OROCOLLO CUEVA MARIO</t>
+          <t>C001517901 - AÑANCA QUISPE OSCAR</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I269" s="2" t="n">
@@ -24331,7 +24331,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -24342,9 +24342,21 @@
       <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr"/>
-      <c r="P269" t="inlineStr"/>
-      <c r="Q269" t="inlineStr"/>
-      <c r="R269" t="inlineStr"/>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S269" t="inlineStr"/>
       <c r="T269" t="inlineStr">
         <is>
@@ -24353,12 +24365,12 @@
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24390,12 +24402,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>C001662599</t>
+          <t>C004161067</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>C001662599 - ZAPATA AGUILAR MERCEDES</t>
+          <t>C004161067 - VENTURA BALDEON JUANA</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -24431,7 +24443,7 @@
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -24566,12 +24578,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>C004161067</t>
+          <t>C001759291</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>C004161067 - VENTURA BALDEON JUANA</t>
+          <t>C001759291 - ALTAMIRANO PEREYRA HAYDEE MIRIAM</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -24618,17 +24630,13 @@
       <c r="S272" t="inlineStr"/>
       <c r="T272" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr"/>
       <c r="V272" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -24660,12 +24668,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>C001759291</t>
+          <t>C001759292</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>C001759291 - ALTAMIRANO PEREYRA HAYDEE MIRIAM</t>
+          <t>C001759292 - RODAS SUAREZ ANITA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -24712,13 +24720,17 @@
       <c r="S273" t="inlineStr"/>
       <c r="T273" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U273" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24740,7 +24752,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -24750,17 +24762,17 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>C001759292</t>
+          <t>C001465182</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>C001759292 - RODAS SUAREZ ANITA</t>
+          <t>C001465182 - LEFONCIO SANCHEZ CRISTIAN ALEXIS</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I274" s="2" t="n">
@@ -24773,7 +24785,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -24784,21 +24796,9 @@
       <c r="M274" t="inlineStr"/>
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
-      <c r="P274" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q274" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R274" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr"/>
       <c r="S274" t="inlineStr"/>
       <c r="T274" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -25462,17 +25462,17 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>C004167639</t>
+          <t>C001759542</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>C004167639 - K &amp; D STORE E.I.R.L.</t>
+          <t>C001759542 - ANA MARIA LUQUE LIPA</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I282" s="2" t="n">
@@ -25485,7 +25485,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -25496,35 +25496,19 @@
       <c r="M282" t="inlineStr"/>
       <c r="N282" t="inlineStr"/>
       <c r="O282" t="inlineStr"/>
-      <c r="P282" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q282" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R282" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P282" t="inlineStr"/>
+      <c r="Q282" t="inlineStr"/>
+      <c r="R282" t="inlineStr"/>
       <c r="S282" t="inlineStr"/>
       <c r="T282" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U282" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr"/>
       <c r="V282" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -25546,7 +25530,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Cliente no usa / no quiere usar el código indicado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -25556,17 +25540,17 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>C004169201</t>
+          <t>C004095661</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>C004169201 - URDIALES GUERRERO BRYAN JUNIOR</t>
+          <t>C004095661 - YOMONA INCIO MIRIAM ANA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I283" s="2" t="n">
@@ -25579,7 +25563,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -25590,9 +25574,21 @@
       <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr"/>
       <c r="O283" t="inlineStr"/>
-      <c r="P283" t="inlineStr"/>
-      <c r="Q283" t="inlineStr"/>
-      <c r="R283" t="inlineStr"/>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S283" t="inlineStr"/>
       <c r="T283" t="inlineStr">
         <is>
@@ -25634,12 +25630,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>C004095661</t>
+          <t>C004043607</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>C004095661 - YOMONA INCIO MIRIAM ANA</t>
+          <t>C004043607 - FLORES LEON MARISELLA DEL CARMEN</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -25686,13 +25682,17 @@
       <c r="S284" t="inlineStr"/>
       <c r="T284" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V284" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25808,7 +25808,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -25818,17 +25818,17 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>C001759542</t>
+          <t>C004167639</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>C001759542 - ANA MARIA LUQUE LIPA</t>
+          <t>C004167639 - K &amp; D STORE E.I.R.L.</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I286" s="2" t="n">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -25852,19 +25852,35 @@
       <c r="M286" t="inlineStr"/>
       <c r="N286" t="inlineStr"/>
       <c r="O286" t="inlineStr"/>
-      <c r="P286" t="inlineStr"/>
-      <c r="Q286" t="inlineStr"/>
-      <c r="R286" t="inlineStr"/>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S286" t="inlineStr"/>
       <c r="T286" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U286" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V286" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25886,7 +25902,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente no usa / no quiere usar el código indicado</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -25896,17 +25912,17 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>C004043607</t>
+          <t>C004169201</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>C004043607 - FLORES LEON MARISELLA DEL CARMEN</t>
+          <t>C004169201 - URDIALES GUERRERO BRYAN JUNIOR</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I287" s="2" t="n">
@@ -25919,7 +25935,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -25930,35 +25946,19 @@
       <c r="M287" t="inlineStr"/>
       <c r="N287" t="inlineStr"/>
       <c r="O287" t="inlineStr"/>
-      <c r="P287" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q287" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R287" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P287" t="inlineStr"/>
+      <c r="Q287" t="inlineStr"/>
+      <c r="R287" t="inlineStr"/>
       <c r="S287" t="inlineStr"/>
       <c r="T287" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U287" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr"/>
       <c r="V287" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -26084,12 +26084,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>C001435529</t>
+          <t>C001562430</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>C001435529 - MARQUINA GUTIERREZ ERIKA PATRICIA</t>
+          <t>C001562430 - CANO YARANGA MIRIAM NOHEMI</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -26125,7 +26125,7 @@
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -26168,7 +26168,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -26178,17 +26178,17 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>C001419064</t>
+          <t>C001544950</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>C001419064 - AZO CONTRERAS ANITA MARCELA</t>
+          <t>C001544950 - VILA DE CAMACHO MARIA ELENA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I290" s="2" t="n">
@@ -26201,7 +26201,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -26212,23 +26212,31 @@
       <c r="M290" t="inlineStr"/>
       <c r="N290" t="inlineStr"/>
       <c r="O290" t="inlineStr"/>
-      <c r="P290" t="inlineStr"/>
-      <c r="Q290" t="inlineStr"/>
-      <c r="R290" t="inlineStr"/>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S290" t="inlineStr"/>
       <c r="T290" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U290" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr"/>
       <c r="V290" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -26344,7 +26352,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -26354,17 +26362,17 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>C001562430</t>
+          <t>C001419064</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>C001562430 - CANO YARANGA MIRIAM NOHEMI</t>
+          <t>C001419064 - AZO CONTRERAS ANITA MARCELA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I292" s="2" t="n">
@@ -26377,7 +26385,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -26388,21 +26396,9 @@
       <c r="M292" t="inlineStr"/>
       <c r="N292" t="inlineStr"/>
       <c r="O292" t="inlineStr"/>
-      <c r="P292" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q292" t="inlineStr">
-        <is>
-          <t>Confirmar pedido</t>
-        </is>
-      </c>
-      <c r="R292" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr"/>
+      <c r="R292" t="inlineStr"/>
       <c r="S292" t="inlineStr"/>
       <c r="T292" t="inlineStr">
         <is>
@@ -26411,12 +26407,12 @@
       </c>
       <c r="U292" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V292" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -26448,12 +26444,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>C001544950</t>
+          <t>C001435529</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>C001544950 - VILA DE CAMACHO MARIA ELENA</t>
+          <t>C001435529 - MARQUINA GUTIERREZ ERIKA PATRICIA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -26500,13 +26496,17 @@
       <c r="S293" t="inlineStr"/>
       <c r="T293" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U293" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26538,12 +26538,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>C001733872</t>
+          <t>C001663961</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>C001733872 - RUPAY FERNANDEZ YÉSICA BEATRÍZ</t>
+          <t>C001663961 - CUEVA GAITAN ELEFANIA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -26574,12 +26574,12 @@
       <c r="O294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q294" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -26595,12 +26595,12 @@
       </c>
       <c r="U294" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V294" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -26726,12 +26726,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>C001663961</t>
+          <t>C001733872</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>C001663961 - CUEVA GAITAN ELEFANIA</t>
+          <t>C001733872 - RUPAY FERNANDEZ YÉSICA BEATRÍZ</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -26762,12 +26762,12 @@
       <c r="O296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -26783,12 +26783,12 @@
       </c>
       <c r="U296" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V296" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -26914,12 +26914,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>C000235635</t>
+          <t>C001172117</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>C000235635 - CONDOR VILCHEZ VILMA PASCUALA</t>
+          <t>C001172117 - TORRES SOLORZANO IGNACIA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -26998,7 +26998,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -27008,17 +27008,17 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>C001389592</t>
+          <t>C000235635</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>C001389592 - JUAREZ CABEZAS VDA DE ALARCON BERTHA</t>
+          <t>C000235635 - CONDOR VILCHEZ VILMA PASCUALA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I299" s="2" t="n">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -27042,19 +27042,35 @@
       <c r="M299" t="inlineStr"/>
       <c r="N299" t="inlineStr"/>
       <c r="O299" t="inlineStr"/>
-      <c r="P299" t="inlineStr"/>
-      <c r="Q299" t="inlineStr"/>
-      <c r="R299" t="inlineStr"/>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S299" t="inlineStr"/>
       <c r="T299" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -27076,7 +27092,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -27086,17 +27102,17 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>C001395870</t>
+          <t>C001389592</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>C001395870 - ROJO ROJAS SAMANDA ROSAURA</t>
+          <t>C001389592 - JUAREZ CABEZAS VDA DE ALARCON BERTHA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I300" s="2" t="n">
@@ -27109,7 +27125,7 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -27120,35 +27136,19 @@
       <c r="M300" t="inlineStr"/>
       <c r="N300" t="inlineStr"/>
       <c r="O300" t="inlineStr"/>
-      <c r="P300" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q300" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R300" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="inlineStr"/>
+      <c r="R300" t="inlineStr"/>
       <c r="S300" t="inlineStr"/>
       <c r="T300" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U300" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr"/>
       <c r="V300" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -27180,12 +27180,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>C001172117</t>
+          <t>C001395870</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>C001172117 - TORRES SOLORZANO IGNACIA</t>
+          <t>C001395870 - ROJO ROJAS SAMANDA ROSAURA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -27221,7 +27221,7 @@
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -27264,7 +27264,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>Persona no tecnológica / tercera edad</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -27274,12 +27274,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>C001759336</t>
+          <t>C001663959</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>C001759336 - LUQUE LIPA LUCIANO ALFREDO</t>
+          <t>C001663959 - YUCRA MERINO NANCY MARILU</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -27314,17 +27314,13 @@
       <c r="S302" t="inlineStr"/>
       <c r="T302" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U302" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr"/>
       <c r="V302" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -27346,7 +27342,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -27356,17 +27352,17 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>C001752700</t>
+          <t>C001665352</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>C001752700 - AYALA GAVILAN DE PEREZ ZOILA PAULINA</t>
+          <t>C001665352 - MENDEZ ANDIA ZAIDA NAAMA</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I303" s="2" t="n">
@@ -27379,7 +27375,7 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -27390,23 +27386,31 @@
       <c r="M303" t="inlineStr"/>
       <c r="N303" t="inlineStr"/>
       <c r="O303" t="inlineStr"/>
-      <c r="P303" t="inlineStr"/>
-      <c r="Q303" t="inlineStr"/>
-      <c r="R303" t="inlineStr"/>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S303" t="inlineStr"/>
       <c r="T303" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U303" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr"/>
       <c r="V303" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -27428,7 +27432,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Persona no tecnológica / tercera edad</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -27438,12 +27442,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>C001663959</t>
+          <t>C001759336</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>C001663959 - YUCRA MERINO NANCY MARILU</t>
+          <t>C001759336 - LUQUE LIPA LUCIANO ALFREDO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -27478,13 +27482,17 @@
       <c r="S304" t="inlineStr"/>
       <c r="T304" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U304" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -27506,7 +27514,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -27516,17 +27524,17 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>C001665352</t>
+          <t>C001752700</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>C001665352 - MENDEZ ANDIA ZAIDA NAAMA</t>
+          <t>C001752700 - AYALA GAVILAN DE PEREZ ZOILA PAULINA</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I305" s="2" t="n">
@@ -27539,7 +27547,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -27550,31 +27558,23 @@
       <c r="M305" t="inlineStr"/>
       <c r="N305" t="inlineStr"/>
       <c r="O305" t="inlineStr"/>
-      <c r="P305" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q305" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R305" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P305" t="inlineStr"/>
+      <c r="Q305" t="inlineStr"/>
+      <c r="R305" t="inlineStr"/>
       <c r="S305" t="inlineStr"/>
       <c r="T305" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U305" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -27880,12 +27880,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>C001759900</t>
+          <t>C001759896</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>C001759900 - AGUILAR QUINONES GABRIEL ERNALDO</t>
+          <t>C001759896 - VILLAVERDE ARIAS EFRAIN JORGE</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -27932,17 +27932,13 @@
       <c r="S309" t="inlineStr"/>
       <c r="T309" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U309" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr"/>
       <c r="V309" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -27974,12 +27970,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>C001759896</t>
+          <t>C001759891</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>C001759896 - VILLAVERDE ARIAS EFRAIN JORGE</t>
+          <t>C001759891 - DIAZ VILLAFANE ERIK EUGENIO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -28015,7 +28011,7 @@
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -28064,12 +28060,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>C001759891</t>
+          <t>C001759900</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>C001759891 - DIAZ VILLAFANE ERIK EUGENIO</t>
+          <t>C001759900 - AGUILAR QUINONES GABRIEL ERNALDO</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -28105,7 +28101,7 @@
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -28116,13 +28112,17 @@
       <c r="S311" t="inlineStr"/>
       <c r="T311" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U311" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -28526,12 +28526,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>C001564298</t>
+          <t>C001531786</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>C001564298 - PINTO CONDORI MARIBEL</t>
+          <t>C001531786 - BRAVO GALLARDO GIOVANNA AZUCENA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -28567,7 +28567,7 @@
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -28583,12 +28583,12 @@
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -28620,12 +28620,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>C001531786</t>
+          <t>C001564298</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>C001531786 - BRAVO GALLARDO GIOVANNA AZUCENA</t>
+          <t>C001564298 - PINTO CONDORI MARIBEL</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -28661,7 +28661,7 @@
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -28677,12 +28677,12 @@
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -28808,12 +28808,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>C001326427</t>
+          <t>C000233799</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>C001326427 - VARGAS PAREDES CELIA</t>
+          <t>C000233799 - DELGADO DELGADO DE VELASQUEZ ANA MARIA</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -28849,7 +28849,7 @@
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -28865,12 +28865,12 @@
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -28892,7 +28892,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -28902,17 +28902,17 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>C001345219</t>
+          <t>C001174025</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>C001345219 - MARQUEZ SUCA EDGAR LEONIDAS</t>
+          <t>C001174025 - JARA MOGOLLON YOWEL SABINO</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I320" s="2" t="n">
@@ -28925,7 +28925,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -28936,9 +28936,21 @@
       <c r="M320" t="inlineStr"/>
       <c r="N320" t="inlineStr"/>
       <c r="O320" t="inlineStr"/>
-      <c r="P320" t="inlineStr"/>
-      <c r="Q320" t="inlineStr"/>
-      <c r="R320" t="inlineStr"/>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S320" t="inlineStr"/>
       <c r="T320" t="inlineStr">
         <is>
@@ -28947,12 +28959,12 @@
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V320" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -29068,7 +29080,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -29078,17 +29090,17 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>C001174025</t>
+          <t>C001345219</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>C001174025 - JARA MOGOLLON YOWEL SABINO</t>
+          <t>C001345219 - MARQUEZ SUCA EDGAR LEONIDAS</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I322" s="2" t="n">
@@ -29101,7 +29113,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -29112,21 +29124,9 @@
       <c r="M322" t="inlineStr"/>
       <c r="N322" t="inlineStr"/>
       <c r="O322" t="inlineStr"/>
-      <c r="P322" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q322" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R322" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P322" t="inlineStr"/>
+      <c r="Q322" t="inlineStr"/>
+      <c r="R322" t="inlineStr"/>
       <c r="S322" t="inlineStr"/>
       <c r="T322" t="inlineStr">
         <is>
@@ -29135,12 +29135,12 @@
       </c>
       <c r="U322" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V322" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29172,12 +29172,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>C000233799</t>
+          <t>C001326427</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>C000233799 - DELGADO DELGADO DE VELASQUEZ ANA MARIA</t>
+          <t>C001326427 - VARGAS PAREDES CELIA</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -29213,7 +29213,7 @@
       </c>
       <c r="Q323" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -29229,12 +29229,12 @@
       </c>
       <c r="U323" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V323" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29442,12 +29442,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>C001681427</t>
+          <t>C004221118</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>C001681427 - MIO MENDOZA MARITZA</t>
+          <t>C004221118 - SUAREZ ROAS KATHERINE JAZMIN</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -29483,7 +29483,7 @@
       </c>
       <c r="Q326" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -29494,13 +29494,17 @@
       <c r="S326" t="inlineStr"/>
       <c r="T326" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U326" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29522,7 +29526,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -29532,17 +29536,17 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>C004221118</t>
+          <t>C004183906</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>C004221118 - SUAREZ ROAS KATHERINE JAZMIN</t>
+          <t>C004183906 - SANABRE PARI NORMA</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I327" s="2" t="n">
@@ -29555,7 +29559,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -29566,21 +29570,9 @@
       <c r="M327" t="inlineStr"/>
       <c r="N327" t="inlineStr"/>
       <c r="O327" t="inlineStr"/>
-      <c r="P327" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R327" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="inlineStr"/>
+      <c r="R327" t="inlineStr"/>
       <c r="S327" t="inlineStr"/>
       <c r="T327" t="inlineStr">
         <is>
@@ -29589,12 +29581,12 @@
       </c>
       <c r="U327" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -29616,7 +29608,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -29626,17 +29618,17 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>C004183906</t>
+          <t>C004184357</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>C004183906 - SANABRE PARI NORMA</t>
+          <t>C004184357 - CRESPIN ROSALES CLARA</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I328" s="2" t="n">
@@ -29649,7 +29641,7 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -29657,12 +29649,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M328" t="inlineStr"/>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N328" t="inlineStr"/>
       <c r="O328" t="inlineStr"/>
-      <c r="P328" t="inlineStr"/>
-      <c r="Q328" t="inlineStr"/>
-      <c r="R328" t="inlineStr"/>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S328" t="inlineStr"/>
       <c r="T328" t="inlineStr">
         <is>
@@ -29671,12 +29679,12 @@
       </c>
       <c r="U328" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V328" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29708,12 +29716,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>C004184357</t>
+          <t>C001638213</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>C004184357 - CRESPIN ROSALES CLARA</t>
+          <t>C001638213 - GAVILAN ZAMORA DE HUAMAN IRIS CLOTILDE</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -29739,11 +29747,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M329" t="inlineStr"/>
       <c r="N329" t="inlineStr"/>
       <c r="O329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
@@ -29753,7 +29757,7 @@
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -29764,17 +29768,13 @@
       <c r="S329" t="inlineStr"/>
       <c r="T329" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U329" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr"/>
       <c r="V329" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -29796,7 +29796,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -29806,17 +29806,17 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>C001638213</t>
+          <t>C001411066</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>C001638213 - GAVILAN ZAMORA DE HUAMAN IRIS CLOTILDE</t>
+          <t>C001411066 - SOLORZANO DE LA CRUZ ODELI ELIZABETH</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I330" s="2" t="n">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -29840,31 +29840,23 @@
       <c r="M330" t="inlineStr"/>
       <c r="N330" t="inlineStr"/>
       <c r="O330" t="inlineStr"/>
-      <c r="P330" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q330" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R330" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P330" t="inlineStr"/>
+      <c r="Q330" t="inlineStr"/>
+      <c r="R330" t="inlineStr"/>
       <c r="S330" t="inlineStr"/>
       <c r="T330" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U330" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V330" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29886,7 +29878,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -29896,17 +29888,17 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>C001411066</t>
+          <t>C001759255</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>C001411066 - SOLORZANO DE LA CRUZ ODELI ELIZABETH</t>
+          <t>C001759255 - VILCA QUISPE DE LEQUERNAQUE MARIA ISABEL</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I331" s="2" t="n">
@@ -29919,7 +29911,7 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -29930,23 +29922,31 @@
       <c r="M331" t="inlineStr"/>
       <c r="N331" t="inlineStr"/>
       <c r="O331" t="inlineStr"/>
-      <c r="P331" t="inlineStr"/>
-      <c r="Q331" t="inlineStr"/>
-      <c r="R331" t="inlineStr"/>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S331" t="inlineStr"/>
       <c r="T331" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U331" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr"/>
       <c r="V331" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -29978,12 +29978,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>C001759255</t>
+          <t>C004183897</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>C001759255 - VILCA QUISPE DE LEQUERNAQUE MARIA ISABEL</t>
+          <t>C004183897 - ACHAHUANCO DIAZ EFRAIN</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -30019,7 +30019,7 @@
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -30030,13 +30030,17 @@
       <c r="S332" t="inlineStr"/>
       <c r="T332" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U332" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -30152,7 +30156,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -30162,17 +30166,17 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>C004183897</t>
+          <t>C004163503</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>C004183897 - ACHAHUANCO DIAZ EFRAIN</t>
+          <t>C004163503 - QUISPE INCA ISABEL</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I334" s="2" t="n">
@@ -30185,7 +30189,7 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -30196,21 +30200,9 @@
       <c r="M334" t="inlineStr"/>
       <c r="N334" t="inlineStr"/>
       <c r="O334" t="inlineStr"/>
-      <c r="P334" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q334" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R334" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P334" t="inlineStr"/>
+      <c r="Q334" t="inlineStr"/>
+      <c r="R334" t="inlineStr"/>
       <c r="S334" t="inlineStr"/>
       <c r="T334" t="inlineStr">
         <is>
@@ -30246,7 +30238,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -30256,17 +30248,17 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>C004163503</t>
+          <t>C004212545</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>C004163503 - QUISPE INCA ISABEL</t>
+          <t>C004212545 - GELDRES VENTOCILLA MARTHA YAKELINE</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I335" s="2" t="n">
@@ -30279,7 +30271,7 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -30290,9 +30282,21 @@
       <c r="M335" t="inlineStr"/>
       <c r="N335" t="inlineStr"/>
       <c r="O335" t="inlineStr"/>
-      <c r="P335" t="inlineStr"/>
-      <c r="Q335" t="inlineStr"/>
-      <c r="R335" t="inlineStr"/>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S335" t="inlineStr"/>
       <c r="T335" t="inlineStr">
         <is>
@@ -30338,12 +30342,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>C004212545</t>
+          <t>C001681427</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>C004212545 - GELDRES VENTOCILLA MARTHA YAKELINE</t>
+          <t>C001681427 - MIO MENDOZA MARITZA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -30379,7 +30383,7 @@
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -30390,17 +30394,13 @@
       <c r="S336" t="inlineStr"/>
       <c r="T336" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U336" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr"/>
       <c r="V336" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>

--- a/excel/d-l-f-medina-rivera-s-a_capacitaciones.xlsx
+++ b/excel/d-l-f-medina-rivera-s-a_capacitaciones.xlsx
@@ -598,12 +598,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C000232321</t>
+          <t>C000232354</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C000232321 - POLINO NIETO CARMEN LORENZA</t>
+          <t>C000232354 - ZU IGA GUERRERO BELLA VIRGINIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C000232354</t>
+          <t>C000232321</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C000232354 - ZU IGA GUERRERO BELLA VIRGINIA</t>
+          <t>C000232321 - POLINO NIETO CARMEN LORENZA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C001646035</t>
+          <t>C001685500</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C001646035 - SUCSO CHUQUIHUAMANI LIZBETH ESTEFANIA</t>
+          <t>C001685500 - FERNANDEZ CARDOZO LEILA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001657596</t>
+          <t>C001670762</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C001657596 - HUARACCALLO HUARSOCCA LUZ</t>
+          <t>C001670762 - DE LA CRUZ AQUIÑO MARLONY FRANDY</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1160,21 +1160,9 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
@@ -1216,12 +1204,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C001685500</t>
+          <t>C001646035</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C001685500 - FERNANDEZ CARDOZO LEILA</t>
+          <t>C001646035 - SUCSO CHUQUIHUAMANI LIZBETH ESTEFANIA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1257,7 +1245,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1296,7 +1284,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1306,17 +1294,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C001670762</t>
+          <t>C001657596</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C001670762 - DE LA CRUZ AQUIÑO MARLONY FRANDY</t>
+          <t>C001657596 - HUARACCALLO HUARSOCCA LUZ</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -1329,7 +1317,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1340,9 +1328,21 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C004095869</t>
+          <t>C004036728</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C004095869 - RAMIREZ HINOSTROZA MAGDA ALEJANDRINA</t>
+          <t>C004036728 - GALLEGOS DE JESUS LOURDES ROCIO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C004036728</t>
+          <t>C004095869</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C004036728 - GALLEGOS DE JESUS LOURDES ROCIO</t>
+          <t>C004095869 - RAMIREZ HINOSTROZA MAGDA ALEJANDRINA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C004178994</t>
+          <t>C004152798</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C004178994 - CORPORACION CM S.A.C.</t>
+          <t>C004152798 - MONTES ALTAMIRANO JOSE ANGEL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1858,7 +1858,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1912,17 +1912,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C004152798</t>
+          <t>C004184739</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C004152798 - MONTES ALTAMIRANO JOSE ANGEL</t>
+          <t>C004184739 - VASQUEZ PEREZ ROSA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1946,21 +1946,9 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
@@ -1992,7 +1980,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2002,17 +1990,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C004184739</t>
+          <t>C004178994</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C004184739 - VASQUEZ PEREZ ROSA</t>
+          <t>C004178994 - CORPORACION CM S.A.C.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
@@ -2025,7 +2013,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2036,9 +2024,21 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C004196968</t>
+          <t>C004193720</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C004196968 - MUCHAYPIÑA FLORES PATRICIA BETZABET</t>
+          <t>C004193720 - NAUTO HUAYHUA JUANA IRIS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2201,11 +2201,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2215,7 +2211,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2264,12 +2260,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C004193720</t>
+          <t>C004196968</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C004193720 - NAUTO HUAYHUA JUANA IRIS</t>
+          <t>C004196968 - MUCHAYPIÑA FLORES PATRICIA BETZABET</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2295,7 +2291,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C004242748</t>
+          <t>C004160693</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C004242748 - VALDERRAMA CARBONERO DEBORAH PATRICIA</t>
+          <t>C004160693 - ARANIBAR CADILLO MARIA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2770,17 +2770,13 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2798,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2812,17 +2808,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C004196887</t>
+          <t>C001762208</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C004196887 - GARCIA RAMIREZ ORLANDO</t>
+          <t>C001762208 - BISA LLENQUE TOMAS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
@@ -2835,7 +2831,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2846,35 +2842,19 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2886,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C004208534</t>
+          <t>C001726599</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C004208534 - HUARACHI FLORES YESSICA VILIA</t>
+          <t>C001726599 - REBOLLEDO PENA MARIA EDELMIRA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2952,7 +2932,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -2986,7 +2966,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2996,17 +2976,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C004160693</t>
+          <t>C001577698</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C004160693 - ARANIBAR CADILLO MARIA</t>
+          <t>C001577698 - ROA CAYLLAHUA VICTOR RAUL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
@@ -3019,7 +2999,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3030,21 +3010,9 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
@@ -3076,7 +3044,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3086,17 +3054,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C001762208</t>
+          <t>C004242748</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C001762208 - BISA LLENQUE TOMAS</t>
+          <t>C004242748 - VALDERRAMA CARBONERO DEBORAH PATRICIA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
@@ -3109,7 +3077,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3120,19 +3088,35 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3148,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C001726599</t>
+          <t>C004208534</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C001726599 - REBOLLEDO PENA MARIA EDELMIRA</t>
+          <t>C004208534 - HUARACHI FLORES YESSICA VILIA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3210,7 +3194,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3244,7 +3228,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3254,17 +3238,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C001577698</t>
+          <t>C004196887</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C001577698 - ROA CAYLLAHUA VICTOR RAUL</t>
+          <t>C004196887 - GARCIA RAMIREZ ORLANDO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -3277,7 +3261,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3288,19 +3272,35 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3332,17 +3332,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C000235424</t>
+          <t>C004173802</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C000235424 - CASTILLO ESPINOZA DE GOMEZ LUCILA</t>
+          <t>C004173802 - GOMEZ DIAZ WALTER DEMETRIO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3366,19 +3366,35 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3416,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3410,17 +3426,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C001274825</t>
+          <t>C000235424</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C001274825 - GUARDADO OCHOA JUAN JOSUE</t>
+          <t>C000235424 - CASTILLO ESPINOZA DE GOMEZ LUCILA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
@@ -3433,7 +3449,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3444,21 +3460,9 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
@@ -3500,12 +3504,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C001634661</t>
+          <t>C001274825</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C001634661 - QUELOPANA DE LA CRUZ JORGE WILLY</t>
+          <t>C001274825 - GUARDADO OCHOA JUAN JOSUE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3590,12 +3594,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C001625923</t>
+          <t>C001634661</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C001625923 - CHACMANA ORE GIOVANNA</t>
+          <t>C001634661 - QUELOPANA DE LA CRUZ JORGE WILLY</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3680,12 +3684,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C001726600</t>
+          <t>C001625923</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C001726600 - GONZALES SALDARRIAGA CESAR AUGUSTO</t>
+          <t>C001625923 - CHACMANA ORE GIOVANNA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3760,7 +3764,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3770,17 +3774,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C001759620</t>
+          <t>C001726600</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C001759620 - YNUMA SAURIN JANETH CECILIA</t>
+          <t>C001726600 - GONZALES SALDARRIAGA CESAR AUGUSTO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
@@ -3793,7 +3797,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3804,23 +3808,31 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3944,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3942,17 +3954,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C004061362</t>
+          <t>C001759620</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C004061362 - RUIZ CHERRE JOSE DENNYS</t>
+          <t>C001759620 - YNUMA SAURIN JANETH CECILIA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
@@ -3965,7 +3977,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3976,31 +3988,23 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4032,12 +4036,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C004173802</t>
+          <t>C004061362</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C004173802 - GOMEZ DIAZ WALTER DEMETRIO</t>
+          <t>C004061362 - RUIZ CHERRE JOSE DENNYS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4084,17 +4088,13 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C000236214</t>
+          <t>C004203419</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C000236214 - MANCCO PEREZ AYDEE LUISA</t>
+          <t>C004203419 - BAZAN CARRERO OSCAR DEMETRIO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -4216,12 +4216,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001011891</t>
+          <t>C000236214</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C001011891 - PACHECO MARCAS DE QUISPE JULIANA</t>
+          <t>C000236214 - MANCCO PEREZ AYDEE LUISA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4268,17 +4268,13 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4310,12 +4306,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001402799</t>
+          <t>C001379326</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C001402799 - DAVILA CAMACHO DORALIZA DEL ROSARIO</t>
+          <t>C001379326 - HARO SILVERIO DIANA ANTONIA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4351,7 +4347,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4404,12 +4400,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001379326</t>
+          <t>C001387536</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C001379326 - HARO SILVERIO DIANA ANTONIA</t>
+          <t>C001387536 - BERRIOS POMA LUCILA CIRILA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4498,12 +4494,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C001265058</t>
+          <t>C001011891</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C001265058 - VALDIVIA LLERENA JACINTO</t>
+          <t>C001011891 - PACHECO MARCAS DE QUISPE JULIANA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4539,7 +4535,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4592,12 +4588,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C001265059</t>
+          <t>C001265058</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C001265059 - CONDORI ASTO DE CHUQUITAIPE EUFEMIA DOMI</t>
+          <t>C001265058 - VALDIVIA LLERENA JACINTO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4644,13 +4640,17 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4682,12 +4682,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C001265116</t>
+          <t>C001265059</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C001265116 - FLORES DE HUANATICO MARCELA</t>
+          <t>C001265059 - CONDORI ASTO DE CHUQUITAIPE EUFEMIA DOMI</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4734,17 +4734,13 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4776,12 +4772,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C001544950</t>
+          <t>C001265116</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C001544950 - VILA DE CAMACHO MARIA ELENA</t>
+          <t>C001265116 - FLORES DE HUANATICO MARCELA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4870,12 +4866,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C001387536</t>
+          <t>C001402799</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C001387536 - BERRIOS POMA LUCILA CIRILA</t>
+          <t>C001402799 - DAVILA CAMACHO DORALIZA DEL ROSARIO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4911,7 +4907,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4964,12 +4960,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C001665735</t>
+          <t>C001544950</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C001665735 - JINEZ MALDONADO SOFIA</t>
+          <t>C001544950 - VILA DE CAMACHO MARIA ELENA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5005,7 +5001,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5016,13 +5012,17 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C001759336</t>
+          <t>C001665735</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C001759336 - LUQUE LIPA LUCIANO ALFREDO</t>
+          <t>C001665735 - JINEZ MALDONADO SOFIA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5106,17 +5106,13 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5148,12 +5144,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C001748448</t>
+          <t>C001759336</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C001748448 - ATANACIO GOMERO LIDIA BRIGITTE</t>
+          <t>C001759336 - LUQUE LIPA LUCIANO ALFREDO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5189,7 +5185,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5242,12 +5238,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C001748948</t>
+          <t>C004094955</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C001748948 - MAURICIO AYALA GIOVANNA MARGARITA</t>
+          <t>C004094955 - MIRANDA PEDROSO YESSENIA FLOR</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5278,12 +5274,12 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Nada dispuesto</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5294,13 +5290,17 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5332,12 +5332,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C004094955</t>
+          <t>C004044635</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C004094955 - MIRANDA PEDROSO YESSENIA FLOR</t>
+          <t>C004044635 - MOREYRA JACOBO MARTIN JESUS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5368,12 +5368,12 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nada dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5384,17 +5384,13 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5412,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5426,17 +5422,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C004044635</t>
+          <t>C004043481</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C004044635 - MOREYRA JACOBO MARTIN JESUS</t>
+          <t>C004043481 - YHA FERNANDEZ JUAN MANUEL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
@@ -5449,7 +5445,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5460,21 +5456,9 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
         <is>
@@ -5506,7 +5490,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5516,17 +5500,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C004043481</t>
+          <t>C004043607</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C004043481 - YHA FERNANDEZ JUAN MANUEL</t>
+          <t>C004043607 - FLORES LEON MARISELLA DEL CARMEN</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
@@ -5539,7 +5523,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5550,19 +5534,35 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No le interesa aprender la app</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5594,17 +5594,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C004043607</t>
+          <t>C001765944</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C004043607 - FLORES LEON MARISELLA DEL CARMEN</t>
+          <t>C001765944 - DUEÑAS LLUCHO SEGUNDO PEDRO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5628,35 +5628,19 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5756,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>No le interesa aprender la app</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5782,17 +5766,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C001765944</t>
+          <t>C001748448</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C001765944 - DUEÑAS LLUCHO SEGUNDO PEDRO</t>
+          <t>C001748448 - ATANACIO GOMERO LIDIA BRIGITTE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
@@ -5805,7 +5789,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5816,19 +5800,35 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5860,17 +5860,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C004174354</t>
+          <t>C001748948</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C004174354 - BAEZ CUTIPA MAURICIA</t>
+          <t>C001748948 - MAURICIO AYALA GIOVANNA MARGARITA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5894,9 +5894,21 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
@@ -5938,12 +5950,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C004164351</t>
+          <t>C004174354</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C004164351 - HERNANDEZ CHOQUE ROSSANA ARANCELLI</t>
+          <t>C004174354 - BAEZ CUTIPA MAURICIA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6006,7 +6018,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6016,17 +6028,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C004203419</t>
+          <t>C004164351</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C004203419 - BAZAN CARRERO OSCAR DEMETRIO</t>
+          <t>C004164351 - HERNANDEZ CHOQUE ROSSANA ARANCELLI</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
@@ -6039,7 +6051,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6050,21 +6062,9 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Apoyo del vendedor</t>
-        </is>
-      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr">
         <is>
@@ -6106,12 +6106,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C004242115</t>
+          <t>C004242724</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C004242115 - CCOÑAS MOSCOSO YOMIRA JANET</t>
+          <t>C004242724 - VILLAVICENCIO NUNJAR MARIA JESUS ANTONIA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6152,23 +6152,19 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6196,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C001759441</t>
+          <t>C004242115</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C001759441 - GONZALES MAGUINA CINZIA GIULIANA</t>
+          <t>C004242115 - CCOÑAS MOSCOSO YOMIRA JANET</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6252,13 +6248,17 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6290,12 +6290,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C001759461</t>
+          <t>C001326551</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C001759461 - LUQUE YANCUNTA CRISTINA ELIZABETH</t>
+          <t>C001326551 - VALDEZ ARQUINEGO JOSE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6342,13 +6342,17 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6374,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6380,17 +6384,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C001759673</t>
+          <t>C001291938</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C001759673 - NAVARRO FUENTES ISABEL HONORIA</t>
+          <t>C001291938 - MERINO MONZON SANTOS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
@@ -6403,7 +6407,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6414,9 +6418,21 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr">
         <is>
@@ -6462,12 +6478,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C001762297</t>
+          <t>C001504119</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>C001762297 - SANCHEZ CASTILLO JENRRY RONALD</t>
+          <t>C001504119 - SINFOROSO ALEGRIA DE SILVERA NELLY LUZ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6498,7 +6514,7 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -6519,12 +6535,12 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6556,12 +6572,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C001766067</t>
+          <t>C001480676</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>C001766067 - CHAMORRO BENDEZU PABLINA</t>
+          <t>C001480676 - YARANGA MARTIN SANDY GLADIS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6613,12 +6629,12 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6666,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C001722681</t>
+          <t>C001481150</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C001722681 - LOYOLA LUNA MARIBEL</t>
+          <t>C001481150 - GUERRA GUTIERREZ DENY RUTH</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6681,21 +6697,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6706,17 +6718,13 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6748,12 +6756,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C004159019</t>
+          <t>C001654069</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C004159019 - BRAVO DIAZ LUZ LEANDRA</t>
+          <t>C001654069 - CAPUÑAY CORNEJO ANTHONY JAMPIERE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6800,17 +6808,13 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6842,12 +6846,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C004181103</t>
+          <t>C001722681</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C004181103 - VARGAS PEREIRA GUILLERMO</t>
+          <t>C001722681 - LOYOLA LUNA MARIBEL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6873,17 +6877,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6894,13 +6902,17 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -6932,12 +6944,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C004180272</t>
+          <t>C001766067</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C004180272 - ANDIA FAUCHEUX YRIS MARIELLA</t>
+          <t>C001766067 - CHAMORRO BENDEZU PABLINA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6973,7 +6985,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6989,12 +7001,12 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7026,12 +7038,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C004242724</t>
+          <t>C001759441</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C004242724 - VILLAVICENCIO NUNJAR MARIA JESUS ANTONIA</t>
+          <t>C001759441 - GONZALES MAGUINA CINZIA GIULIANA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7072,7 +7084,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S74" t="inlineStr"/>
@@ -7116,12 +7128,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C004236992</t>
+          <t>C001759461</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C004236992 - CARHUAPOMA INGA IRMA</t>
+          <t>C001759461 - LUQUE YANCUNTA CRISTINA ELIZABETH</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7168,17 +7180,13 @@
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7208,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7210,17 +7218,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C001504119</t>
+          <t>C001759673</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C001504119 - SINFOROSO ALEGRIA DE SILVERA NELLY LUZ</t>
+          <t>C001759673 - NAVARRO FUENTES ISABEL HONORIA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
@@ -7233,7 +7241,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7244,21 +7252,9 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr">
         <is>
@@ -7267,12 +7263,12 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7300,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C001480676</t>
+          <t>C001762297</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C001480676 - YARANGA MARTIN SANDY GLADIS</t>
+          <t>C001762297 - SANCHEZ CASTILLO JENRRY RONALD</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7345,7 +7341,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7361,12 +7357,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7398,12 +7394,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C001481150</t>
+          <t>C004159019</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C001481150 - GUERRA GUTIERREZ DENY RUTH</t>
+          <t>C004159019 - BRAVO DIAZ LUZ LEANDRA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7434,7 +7430,7 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -7450,13 +7446,17 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C001654069</t>
+          <t>C004180272</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C001654069 - CAPUÑAY CORNEJO ANTHONY JAMPIERE</t>
+          <t>C004180272 - ANDIA FAUCHEUX YRIS MARIELLA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7540,13 +7540,17 @@
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7582,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C001326551</t>
+          <t>C004181103</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>C001326551 - VALDEZ ARQUINEGO JOSE</t>
+          <t>C004181103 - VARGAS PEREIRA GUILLERMO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7630,17 +7634,13 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C001291938</t>
+          <t>C004236992</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>C001291938 - MERINO MONZON SANTOS</t>
+          <t>C004236992 - CARHUAPOMA INGA IRMA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C001572036</t>
+          <t>C004142651</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>C001572036 - CHOMBO ORTIZ JESSICA FERNANDA</t>
+          <t>C004142651 - COSAR CAPARACHIN ESPIRITA BERTHA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C004142651</t>
+          <t>C001572036</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>C004142651 - COSAR CAPARACHIN ESPIRITA BERTHA</t>
+          <t>C001572036 - CHOMBO ORTIZ JESSICA FERNANDA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -8584,12 +8584,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C004051473</t>
+          <t>C004165733</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>C004051473 - RAMOS MAMANI BENEDICTO</t>
+          <t>C004165733 - FERNANDEZ VASQUEZ ANGEL GABRIEL</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8636,17 +8636,13 @@
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -8678,12 +8674,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C004165733</t>
+          <t>C004051473</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>C004165733 - FERNANDEZ VASQUEZ ANGEL GABRIEL</t>
+          <t>C004051473 - RAMOS MAMANI BENEDICTO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8730,13 +8726,17 @@
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -8956,12 +8956,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C001474177</t>
+          <t>C001402353</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>C001474177 - QUISPE HUAMAN JOSE LUIS</t>
+          <t>C001402353 - BARRETO ROJAS JOSE LUIS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -9046,12 +9046,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C001402353</t>
+          <t>C001563636</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>C001402353 - BARRETO ROJAS JOSE LUIS</t>
+          <t>C001563636 - MENDOZA BACCA ETELVINA JESUS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C001554354</t>
+          <t>C001617965</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C001554354 - PANDURO CRUZ SANDRA LUZ</t>
+          <t>C001617965 - RAVELLO NEGRON MAXIMILIANO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9177,28 +9177,24 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9230,12 +9226,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C001563636</t>
+          <t>C001554354</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>C001563636 - MENDOZA BACCA ETELVINA JESUS</t>
+          <t>C001554354 - PANDURO CRUZ SANDRA LUZ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9271,7 +9267,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -9282,13 +9278,17 @@
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C001617965</t>
+          <t>C001474177</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C001617965 - RAVELLO NEGRON MAXIMILIANO</t>
+          <t>C001474177 - QUISPE HUAMAN JOSE LUIS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Más capacitación</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S99" t="inlineStr"/>
@@ -9410,12 +9410,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C001713132</t>
+          <t>C001717695</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>C001713132 - JULCA FABIAN RONAL</t>
+          <t>C001717695 - MILLONES LOPEZ MARIA JESUS</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9462,17 +9462,13 @@
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9490,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Persona no tecnológica / tercera edad</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -9504,17 +9500,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C001743137</t>
+          <t>C001718083</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>C001743137 - MGD ASESORES Y CONSULTORES S.A.C.</t>
+          <t>C001718083 - RAMOS SALDARRIAGA SARITA MILAGROS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
@@ -9527,7 +9523,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -9538,35 +9534,19 @@
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9598,12 +9578,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>C001717695</t>
+          <t>C001713132</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>C001717695 - MILLONES LOPEZ MARIA JESUS</t>
+          <t>C001713132 - JULCA FABIAN RONAL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9650,13 +9630,17 @@
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9662,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Persona no tecnológica / tercera edad</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9688,17 +9672,17 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>C001718083</t>
+          <t>C001743137</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>C001718083 - RAMOS SALDARRIAGA SARITA MILAGROS</t>
+          <t>C001743137 - MGD ASESORES Y CONSULTORES S.A.C.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
@@ -9711,7 +9695,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -9722,19 +9706,35 @@
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>C001740024</t>
+          <t>C004049602</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>C001740024 - MORAN VACA BETTY AURORA</t>
+          <t>C004049602 - CALLIRGOS RODRIGUEZ INES</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -10272,17 +10272,13 @@
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10314,12 +10310,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>C001766040</t>
+          <t>C001740024</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>C001766040 - ALBUJAR RAMIREZ ERIKA LUCIA</t>
+          <t>C001740024 - MORAN VACA BETTY AURORA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10371,12 +10367,12 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -10408,12 +10404,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>C004049602</t>
+          <t>C001766040</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>C004049602 - CALLIRGOS RODRIGUEZ INES</t>
+          <t>C001766040 - ALBUJAR RAMIREZ ERIKA LUCIA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10449,7 +10445,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -10460,13 +10456,17 @@
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10498,12 +10498,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>C004242752</t>
+          <t>C001568676</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>C004242752 - TORRES SHIMIZU SHARON AKEMI</t>
+          <t>C001568676 - CHIPURGO TORRES MILAGROS MARITZA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>C004239739</t>
+          <t>C001715124</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>C004239739 - PEÑA QUISPE POL NELSON</t>
+          <t>C001715124 - MURRIETA SANDOVAL DEYANIRA VENUS MILAGRO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10644,17 +10644,13 @@
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10686,12 +10682,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>C004216600</t>
+          <t>C001763295</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>C004216600 - MEZA GARAY YESSICA JACQUELINE</t>
+          <t>C001763295 - MACHUCA MARQUEZ MILAGROS MERCEDES</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10727,7 +10723,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -10743,12 +10739,12 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>Vendedor</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>SI - Vendedor hizo pedido (no autogestionado)</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10776,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>C004097943</t>
+          <t>C004039089</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>C004097943 - BARLETTI CHAVEZ JOSSELYN IVONNE</t>
+          <t>C004039089 - SAAVEDRA LUCANO SEGUNDO CESAR</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10821,7 +10817,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -10832,17 +10828,13 @@
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10874,12 +10866,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>C001763295</t>
+          <t>C004097943</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>C001763295 - MACHUCA MARQUEZ MILAGROS MERCEDES</t>
+          <t>C004097943 - BARLETTI CHAVEZ JOSSELYN IVONNE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10915,7 +10907,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -10968,12 +10960,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C004039089</t>
+          <t>C004242752</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>C004039089 - SAAVEDRA LUCANO SEGUNDO CESAR</t>
+          <t>C004242752 - TORRES SHIMIZU SHARON AKEMI</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -11020,13 +11012,17 @@
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11058,12 +11054,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C001715124</t>
+          <t>C004216600</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>C001715124 - MURRIETA SANDOVAL DEYANIRA VENUS MILAGRO</t>
+          <t>C004216600 - MEZA GARAY YESSICA JACQUELINE</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11099,7 +11095,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -11110,13 +11106,17 @@
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Vendedor</t>
+        </is>
+      </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Vendedor hizo pedido (no autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11148,12 +11148,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>C001568676</t>
+          <t>C004239739</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>C001568676 - CHIPURGO TORRES MILAGROS MARITZA</t>
+          <t>C004239739 - PEÑA QUISPE POL NELSON</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -15210,12 +15210,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>C001368673</t>
+          <t>C001360767</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>C001368673 - DE LA CRUZ CAHUANA DANTE</t>
+          <t>C001360767 - CORPORACION MERCANTIL DECAR S.A.C.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>C001326934</t>
+          <t>C001364446</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>C001326934 - SOLAR CAMPOS JUAN CARLOS</t>
+          <t>C001364446 - DOMINGUEZ LOPEZ MARTIN ENRIQUE</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -15398,12 +15398,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>C001360767</t>
+          <t>C001326934</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>C001360767 - CORPORACION MERCANTIL DECAR S.A.C.</t>
+          <t>C001326934 - SOLAR CAMPOS JUAN CARLOS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -15492,17 +15492,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>C001364446</t>
+          <t>C001405660</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>C001364446 - DOMINGUEZ LOPEZ MARTIN ENRIQUE</t>
+          <t>C001405660 - MENDOZA TARAZONA ROSARIO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -15526,21 +15526,9 @@
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
       <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr">
         <is>
@@ -15576,7 +15564,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -15586,17 +15574,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>C001405660</t>
+          <t>C001368673</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>C001405660 - MENDOZA TARAZONA ROSARIO</t>
+          <t>C001368673 - DE LA CRUZ CAHUANA DANTE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
@@ -15609,7 +15597,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -15620,9 +15608,21 @@
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
-      <c r="R168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr">
         <is>
@@ -16952,12 +16952,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>C001742612</t>
+          <t>C001763762</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>C001742612 - TORIBIO CUYA SONIA</t>
+          <t>C001763762 - VELASQUE CURPOS REYNECITO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -17004,17 +17004,13 @@
       <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -17046,12 +17042,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>C001749566</t>
+          <t>C001742612</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>C001749566 - CONDOR CONDOR HENRY EDUARDO</t>
+          <t>C001742612 - TORIBIO CUYA SONIA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -17087,7 +17083,7 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -17140,12 +17136,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>C001763762</t>
+          <t>C001749566</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>C001763762 - VELASQUE CURPOS REYNECITO</t>
+          <t>C001749566 - CONDOR CONDOR HENRY EDUARDO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -17192,13 +17188,17 @@
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U185" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -18966,7 +18966,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -18976,17 +18976,17 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>C001550829</t>
+          <t>C001683341</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>C001550829 - SIFUENTES DIAZ MAGDA MAGDALENA</t>
+          <t>C001683341 - CRUZ LUCIANA</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I205" s="2" t="n">
@@ -18999,7 +18999,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -19010,9 +19010,21 @@
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
-      <c r="R205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S205" t="inlineStr"/>
       <c r="T205" t="inlineStr">
         <is>
@@ -19048,7 +19060,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -19058,17 +19070,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>C001683341</t>
+          <t>C001569164</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>C001683341 - CRUZ LUCIANA</t>
+          <t>C001569164 - CHAMAYA MARQUEZ REYNERIO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I206" s="2" t="n">
@@ -19081,7 +19093,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -19092,21 +19104,9 @@
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -19152,17 +19152,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>C001638076</t>
+          <t>C001573340</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>C001638076 - BERAUN ALVA MARCO LIBIO</t>
+          <t>C001573340 - CASTILLO CORDOVA ELIAS</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I207" s="2" t="n">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -19186,9 +19186,21 @@
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr"/>
-      <c r="R207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr">
         <is>
@@ -19224,7 +19236,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -19234,12 +19246,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>C001569164</t>
+          <t>C001550829</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>C001569164 - CHAMAYA MARQUEZ REYNERIO</t>
+          <t>C001550829 - SIFUENTES DIAZ MAGDA MAGDALENA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -19316,12 +19328,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>C001573340</t>
+          <t>C001576586</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>C001573340 - CASTILLO CORDOVA ELIAS</t>
+          <t>C001576586 - MADERO ALAYO ELIZABETH MARIA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -19357,7 +19369,7 @@
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
@@ -19400,7 +19412,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -19410,17 +19422,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>C001576586</t>
+          <t>C001638076</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>C001576586 - MADERO ALAYO ELIZABETH MARIA</t>
+          <t>C001638076 - BERAUN ALVA MARCO LIBIO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I210" s="2" t="n">
@@ -19433,7 +19445,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -19444,21 +19456,9 @@
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R210" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
       <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr">
         <is>
@@ -19504,12 +19504,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>C001749655</t>
+          <t>C001658239</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>C001749655 - REYES CADENILLAS SIMONNE JAEL</t>
+          <t>C001658239 - GOMEZ ENRIQUEZ LUZ VIOLETA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -19556,13 +19556,17 @@
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U211" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19588,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -19594,17 +19598,17 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>C001745477</t>
+          <t>C001749655</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>C001745477 - VEGA PEREDA CHABUCA MAVILA</t>
+          <t>C001749655 - REYES CADENILLAS SIMONNE JAEL</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I212" s="2" t="n">
@@ -19617,7 +19621,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -19628,9 +19632,21 @@
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
-      <c r="R212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S212" t="inlineStr"/>
       <c r="T212" t="inlineStr">
         <is>
@@ -19860,12 +19876,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>C001658239</t>
+          <t>C004024351</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>C001658239 - GOMEZ ENRIQUEZ LUZ VIOLETA</t>
+          <t>C004024351 - ROJAS TIRADO ROBIN LENIN</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -19901,7 +19917,7 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
@@ -19954,12 +19970,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>C004039136</t>
+          <t>C001759239</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>C004039136 - RODRIGUEZ GONZALES CARLOS JESUS</t>
+          <t>C001759239 - GAMONAL ORELLANA RICARDINA DOMINGA</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -20038,7 +20054,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Persona no tecnológica / tercera edad</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -20048,17 +20064,17 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>C004024351</t>
+          <t>C001759240</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>C004024351 - ROJAS TIRADO ROBIN LENIN</t>
+          <t>C001759240 - PARIGUANA SARAVIA MARIA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I217" s="2" t="n">
@@ -20071,7 +20087,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -20082,35 +20098,19 @@
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R217" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
       <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -20142,12 +20142,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>C001759239</t>
+          <t>C001759251</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>C001759239 - GAMONAL ORELLANA RICARDINA DOMINGA</t>
+          <t>C001759251 - CHISE OROZCO ROSA MARIA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -20178,12 +20178,12 @@
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Persona no tecnológica / tercera edad</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -20236,17 +20236,17 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>C001759240</t>
+          <t>C001759624</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>C001759240 - PARIGUANA SARAVIA MARIA</t>
+          <t>C001759624 - CEBREROS CORONACION GLORIA MARINA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I219" s="2" t="n">
@@ -20259,7 +20259,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -20270,19 +20270,35 @@
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
-      <c r="R219" t="inlineStr"/>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U219" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -20314,12 +20330,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>C001759251</t>
+          <t>C004039136</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>C001759251 - CHISE OROZCO ROSA MARIA</t>
+          <t>C004039136 - RODRIGUEZ GONZALES CARLOS JESUS</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -20350,12 +20366,12 @@
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -20398,7 +20414,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -20408,17 +20424,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>C001759624</t>
+          <t>C001745477</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>C001759624 - CEBREROS CORONACION GLORIA MARINA</t>
+          <t>C001745477 - VEGA PEREDA CHABUCA MAVILA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I221" s="2" t="n">
@@ -20431,7 +20447,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -20442,35 +20458,19 @@
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R221" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
       <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr"/>
       <c r="V221" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -20592,12 +20592,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>C004172053</t>
+          <t>C004177833</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>C004172053 - HUAYAC ESCOBAR DALILA</t>
+          <t>C004177833 - SARAVIA CASTILLA MARTHA LUZ</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -20637,12 +20637,12 @@
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -20674,12 +20674,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>C004177833</t>
+          <t>C004172053</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>C004177833 - SARAVIA CASTILLA MARTHA LUZ</t>
+          <t>C004172053 - HUAYAC ESCOBAR DALILA</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -20719,12 +20719,12 @@
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V224" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -22038,7 +22038,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Persona no tecnológica / tercera edad</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -22048,17 +22048,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>C001630592</t>
+          <t>C001664822</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>C001630592 - ESPINOZA ALMINAGORDA EVA</t>
+          <t>C001664822 - RISCO VEGA FELICITAS</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I239" s="2" t="n">
@@ -22071,7 +22071,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -22082,35 +22082,19 @@
       <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q239" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R239" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -22132,7 +22116,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Persona no tecnológica / tercera edad</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -22142,17 +22126,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>C001664822</t>
+          <t>C001630592</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>C001664822 - RISCO VEGA FELICITAS</t>
+          <t>C001630592 - ESPINOZA ALMINAGORDA EVA</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I240" s="2" t="n">
@@ -22165,7 +22149,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -22176,19 +22160,35 @@
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr"/>
-      <c r="R240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U240" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22220,12 +22220,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>C001691427</t>
+          <t>C001722364</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>C001691427 - APAZA SORIA EDWIN CHRISTIAN</t>
+          <t>C001722364 - VILLANUEVA VARGAS MARISA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>C001722364</t>
+          <t>C001691427</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>C001722364 - VILLANUEVA VARGAS MARISA</t>
+          <t>C001691427 - APAZA SORIA EDWIN CHRISTIAN</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -22355,7 +22355,7 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
@@ -22408,12 +22408,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>C001748740</t>
+          <t>C001723315</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>C001748740 - PALACIOS FARFAN YSABEL</t>
+          <t>C001723315 - VERA ZAPATA YULIMER</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -22448,17 +22448,13 @@
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr"/>
       <c r="V243" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -22480,7 +22476,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -22490,17 +22486,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>C001754511</t>
+          <t>C001724853</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>C001754511 - REYES HERNANDEZ JESUS OSWALDO</t>
+          <t>C001724853 - CUMPA GONZALES YRIS</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I244" s="2" t="n">
@@ -22513,7 +22509,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -22524,9 +22520,21 @@
       <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
-      <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
-      <c r="R244" t="inlineStr"/>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S244" t="inlineStr"/>
       <c r="T244" t="inlineStr">
         <is>
@@ -22562,7 +22570,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -22572,17 +22580,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>C001723315</t>
+          <t>C001734390</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>C001723315 - VERA ZAPATA YULIMER</t>
+          <t>C001734390 - TARAZONA FIGUEROA ERIKA LUZ</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I245" s="2" t="n">
@@ -22595,7 +22603,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -22606,19 +22614,35 @@
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
-      <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
-      <c r="R245" t="inlineStr"/>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S245" t="inlineStr"/>
       <c r="T245" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U245" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22664,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -22650,17 +22674,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>C001724853</t>
+          <t>C001748740</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>C001724853 - CUMPA GONZALES YRIS</t>
+          <t>C001748740 - PALACIOS FARFAN YSABEL</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I246" s="2" t="n">
@@ -22673,7 +22697,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -22684,21 +22708,9 @@
       <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
-      <c r="P246" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q246" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R246" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr"/>
       <c r="T246" t="inlineStr">
         <is>
@@ -22734,7 +22746,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -22744,17 +22756,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>C001734390</t>
+          <t>C001754511</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>C001734390 - TARAZONA FIGUEROA ERIKA LUZ</t>
+          <t>C001754511 - REYES HERNANDEZ JESUS OSWALDO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I247" s="2" t="n">
@@ -22767,7 +22779,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -22778,21 +22790,9 @@
       <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
-      <c r="P247" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R247" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr"/>
       <c r="T247" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -23292,17 +23292,17 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>C004162088</t>
+          <t>C004178724</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>C004162088 - JULCA VEGA CARMEN AMELIA</t>
+          <t>C004178724 - DOMINGUEZ INGA ROSARIA</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I253" s="2" t="n">
@@ -23315,7 +23315,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -23326,9 +23326,21 @@
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
-      <c r="P253" t="inlineStr"/>
-      <c r="Q253" t="inlineStr"/>
-      <c r="R253" t="inlineStr"/>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr">
         <is>
@@ -23337,12 +23349,12 @@
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -23458,7 +23470,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -23468,17 +23480,17 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>C004178724</t>
+          <t>C004162088</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>C004178724 - DOMINGUEZ INGA ROSARIA</t>
+          <t>C004162088 - JULCA VEGA CARMEN AMELIA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I255" s="2" t="n">
@@ -23491,7 +23503,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -23502,21 +23514,9 @@
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr"/>
-      <c r="P255" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q255" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R255" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
+      <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr"/>
       <c r="T255" t="inlineStr">
         <is>
@@ -23525,12 +23525,12 @@
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -24466,12 +24466,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>C001759170</t>
+          <t>C001746515</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>C001759170 - VARGAS ZAMUDIO JUANA</t>
+          <t>C001746515 - MARIN GARCIA LILI MARDELI</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -24502,12 +24502,12 @@
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -24560,12 +24560,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>C001746515</t>
+          <t>C001759170</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>C001746515 - MARIN GARCIA LILI MARDELI</t>
+          <t>C001759170 - VARGAS ZAMUDIO JUANA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -24596,12 +24596,12 @@
       <c r="O267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -25284,12 +25284,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>C004191510</t>
+          <t>C004168864</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>C004191510 - DAMIAN SANTISTEBAN ESTHER</t>
+          <t>C004168864 - HUAMANI CARRIZALES MARY LUZ</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -25325,7 +25325,7 @@
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -25378,12 +25378,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>C004168864</t>
+          <t>C004206805</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>C004168864 - HUAMANI CARRIZALES MARY LUZ</t>
+          <t>C004206805 - ACARO CALLE WILMER</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -25472,12 +25472,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>C004206805</t>
+          <t>C004191510</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>C004206805 - ACARO CALLE WILMER</t>
+          <t>C004191510 - DAMIAN SANTISTEBAN ESTHER</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Tuvo una mala experiencia previa usando Diadía</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -25566,12 +25566,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>C001693184</t>
+          <t>C001678803</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>C001693184 - CALVAY CALVAY NATIVA</t>
+          <t>C001678803 - SULCA HUACAUSE LUISA FLOR</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -25611,12 +25611,12 @@
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V278" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -25638,7 +25638,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>Tuvo una mala experiencia previa usando Diadía</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -25648,12 +25648,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>C001678803</t>
+          <t>C001693184</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>C001678803 - SULCA HUACAUSE LUISA FLOR</t>
+          <t>C001693184 - CALVAY CALVAY NATIVA</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -25693,12 +25693,12 @@
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25720,7 +25720,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -25730,17 +25730,17 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>C001726287</t>
+          <t>C001759230</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>C001726287 - CRIOLLO PARDO MARTIN ALEXANDER</t>
+          <t>C001759230 - FLORES CUEVA TEODORICO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I280" s="2" t="n">
@@ -25753,7 +25753,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -25764,9 +25764,21 @@
       <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr"/>
-      <c r="P280" t="inlineStr"/>
-      <c r="Q280" t="inlineStr"/>
-      <c r="R280" t="inlineStr"/>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S280" t="inlineStr"/>
       <c r="T280" t="inlineStr">
         <is>
@@ -25775,12 +25787,12 @@
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V280" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -25812,12 +25824,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>C001759230</t>
+          <t>C001759344</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>C001759230 - FLORES CUEVA TEODORICO</t>
+          <t>C001759344 - TAVARA HUAMAN MELVA YANET</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -25853,7 +25865,7 @@
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -25906,12 +25918,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>C001759344</t>
+          <t>C001759933</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>C001759344 - TAVARA HUAMAN MELVA YANET</t>
+          <t>C001759933 - HIJAR ZEVALLOS MAGDALENA URBANA</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -25990,7 +26002,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -26000,17 +26012,17 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>C001759933</t>
+          <t>C001726287</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>C001759933 - HIJAR ZEVALLOS MAGDALENA URBANA</t>
+          <t>C001726287 - CRIOLLO PARDO MARTIN ALEXANDER</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I283" s="2" t="n">
@@ -26023,7 +26035,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -26034,21 +26046,9 @@
       <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr"/>
       <c r="O283" t="inlineStr"/>
-      <c r="P283" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q283" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R283" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr"/>
+      <c r="R283" t="inlineStr"/>
       <c r="S283" t="inlineStr"/>
       <c r="T283" t="inlineStr">
         <is>
@@ -26057,12 +26057,12 @@
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -26658,12 +26658,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>C001002927</t>
+          <t>C001157290</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>C001002927 - ALEJANDRO GRANADOS EUSEBIO FERRER</t>
+          <t>C001157290 - TORRES HUAMANI HERMINIA CARMEN</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -26752,12 +26752,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>C001011370</t>
+          <t>C001002927</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>C001011370 - LEON ACUÑA JOSE ANTONIO</t>
+          <t>C001002927 - ALEJANDRO GRANADOS EUSEBIO FERRER</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>C001157290</t>
+          <t>C001011370</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>C001157290 - TORRES HUAMANI HERMINIA CARMEN</t>
+          <t>C001011370 - LEON ACUÑA JOSE ANTONIO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -27762,12 +27762,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>C001517901</t>
+          <t>C004179671</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>C001517901 - AÑANCA QUISPE OSCAR</t>
+          <t>C004179671 - CHANAME CAMACHO MARIA LEONOR</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -27803,7 +27803,7 @@
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -27856,17 +27856,17 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>C001660450</t>
+          <t>C001679254</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>C001660450 - OROCOLLO CUEVA MARIO</t>
+          <t>C001679254 - LUQUE HUAMAN JAVIER REYNALDO</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I303" s="2" t="n">
@@ -27879,7 +27879,7 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -27890,9 +27890,21 @@
       <c r="M303" t="inlineStr"/>
       <c r="N303" t="inlineStr"/>
       <c r="O303" t="inlineStr"/>
-      <c r="P303" t="inlineStr"/>
-      <c r="Q303" t="inlineStr"/>
-      <c r="R303" t="inlineStr"/>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S303" t="inlineStr"/>
       <c r="T303" t="inlineStr">
         <is>
@@ -27901,12 +27913,12 @@
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -27928,7 +27940,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -27938,17 +27950,17 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>C001662599</t>
+          <t>C001660450</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>C001662599 - ZAPATA AGUILAR MERCEDES</t>
+          <t>C001660450 - OROCOLLO CUEVA MARIO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I304" s="2" t="n">
@@ -27961,7 +27973,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -27972,21 +27984,9 @@
       <c r="M304" t="inlineStr"/>
       <c r="N304" t="inlineStr"/>
       <c r="O304" t="inlineStr"/>
-      <c r="P304" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q304" t="inlineStr">
-        <is>
-          <t>Confirmar pedido</t>
-        </is>
-      </c>
-      <c r="R304" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P304" t="inlineStr"/>
+      <c r="Q304" t="inlineStr"/>
+      <c r="R304" t="inlineStr"/>
       <c r="S304" t="inlineStr"/>
       <c r="T304" t="inlineStr">
         <is>
@@ -27995,12 +27995,12 @@
       </c>
       <c r="U304" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V304" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -28032,17 +28032,17 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>C001577690</t>
+          <t>C001662599</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>C001577690 - CHAVEZ DE CRUZATT FELICITA</t>
+          <t>C001662599 - ZAPATA AGUILAR MERCEDES</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I305" s="2" t="n">
@@ -28055,7 +28055,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -28066,9 +28066,21 @@
       <c r="M305" t="inlineStr"/>
       <c r="N305" t="inlineStr"/>
       <c r="O305" t="inlineStr"/>
-      <c r="P305" t="inlineStr"/>
-      <c r="Q305" t="inlineStr"/>
-      <c r="R305" t="inlineStr"/>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S305" t="inlineStr"/>
       <c r="T305" t="inlineStr">
         <is>
@@ -28104,7 +28116,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -28114,17 +28126,17 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>C001578094</t>
+          <t>C001577690</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>C001578094 - ZAVALETA CACHIQUE DE CUADROS LILIANA</t>
+          <t>C001577690 - CHAVEZ DE CRUZATT FELICITA</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I306" s="2" t="n">
@@ -28137,7 +28149,7 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -28148,21 +28160,9 @@
       <c r="M306" t="inlineStr"/>
       <c r="N306" t="inlineStr"/>
       <c r="O306" t="inlineStr"/>
-      <c r="P306" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q306" t="inlineStr">
-        <is>
-          <t>Confirmar pedido</t>
-        </is>
-      </c>
-      <c r="R306" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P306" t="inlineStr"/>
+      <c r="Q306" t="inlineStr"/>
+      <c r="R306" t="inlineStr"/>
       <c r="S306" t="inlineStr"/>
       <c r="T306" t="inlineStr">
         <is>
@@ -28208,12 +28208,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>C001679254</t>
+          <t>C001578094</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>C001679254 - LUQUE HUAMAN JAVIER REYNALDO</t>
+          <t>C001578094 - ZAVALETA CACHIQUE DE CUADROS LILIANA</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -28249,7 +28249,7 @@
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -28386,7 +28386,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -28396,17 +28396,17 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>C001759291</t>
+          <t>C004100895</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>C001759291 - ALTAMIRANO PEREYRA HAYDEE MIRIAM</t>
+          <t>C004100895 - BERNAL RAMOS JUANA ARACELY</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I309" s="2" t="n">
@@ -28419,7 +28419,7 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -28430,31 +28430,23 @@
       <c r="M309" t="inlineStr"/>
       <c r="N309" t="inlineStr"/>
       <c r="O309" t="inlineStr"/>
-      <c r="P309" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q309" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="R309" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P309" t="inlineStr"/>
+      <c r="Q309" t="inlineStr"/>
+      <c r="R309" t="inlineStr"/>
       <c r="S309" t="inlineStr"/>
       <c r="T309" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U309" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -28486,12 +28478,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>C001759292</t>
+          <t>C004161067</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>C001759292 - RODAS SUAREZ ANITA</t>
+          <t>C004161067 - VENTURA BALDEON JUANA</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -28580,12 +28572,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>C004179671</t>
+          <t>C001759291</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>C004179671 - CHANAME CAMACHO MARIA LEONOR</t>
+          <t>C001759291 - ALTAMIRANO PEREYRA HAYDEE MIRIAM</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -28632,17 +28624,13 @@
       <c r="S311" t="inlineStr"/>
       <c r="T311" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U311" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr"/>
       <c r="V311" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -28664,7 +28652,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -28674,17 +28662,17 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>C004100895</t>
+          <t>C001759292</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>C004100895 - BERNAL RAMOS JUANA ARACELY</t>
+          <t>C001759292 - RODAS SUAREZ ANITA</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I312" s="2" t="n">
@@ -28697,7 +28685,7 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -28708,9 +28696,21 @@
       <c r="M312" t="inlineStr"/>
       <c r="N312" t="inlineStr"/>
       <c r="O312" t="inlineStr"/>
-      <c r="P312" t="inlineStr"/>
-      <c r="Q312" t="inlineStr"/>
-      <c r="R312" t="inlineStr"/>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S312" t="inlineStr"/>
       <c r="T312" t="inlineStr">
         <is>
@@ -28756,12 +28756,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>C004161067</t>
+          <t>C000232398</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>C004161067 - VENTURA BALDEON JUANA</t>
+          <t>C000232398 - BRAVO HUANACO ALEJANDRINA ALFONSA</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -28792,12 +28792,12 @@
       <c r="O313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -28808,17 +28808,13 @@
       <c r="S313" t="inlineStr"/>
       <c r="T313" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U313" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr"/>
       <c r="V313" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -28840,7 +28836,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -28850,12 +28846,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>C001465182</t>
+          <t>C000232420</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>C001465182 - LEFONCIO SANCHEZ CRISTIAN ALEXIS</t>
+          <t>C000232420 - SANTISTEBAN TEJADA MANUEL</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -28922,7 +28918,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -28932,17 +28928,17 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>C001403722</t>
+          <t>C000232429</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>C001403722 - SALLUCA JIMENEZ JORGE JESUS</t>
+          <t>C000232429 - TICONA MOYA ELISA</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I315" s="2" t="n">
@@ -28955,7 +28951,7 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -28966,9 +28962,21 @@
       <c r="M315" t="inlineStr"/>
       <c r="N315" t="inlineStr"/>
       <c r="O315" t="inlineStr"/>
-      <c r="P315" t="inlineStr"/>
-      <c r="Q315" t="inlineStr"/>
-      <c r="R315" t="inlineStr"/>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S315" t="inlineStr"/>
       <c r="T315" t="inlineStr">
         <is>
@@ -29004,7 +29012,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -29014,17 +29022,17 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>C001385811</t>
+          <t>C000232644</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>C001385811 - CRUZZATT FIGUEROA SALUTINIANO</t>
+          <t>C000232644 - CHARQUI CRUZ NORMA LOLA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I316" s="2" t="n">
@@ -29037,7 +29045,7 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -29048,9 +29056,21 @@
       <c r="M316" t="inlineStr"/>
       <c r="N316" t="inlineStr"/>
       <c r="O316" t="inlineStr"/>
-      <c r="P316" t="inlineStr"/>
-      <c r="Q316" t="inlineStr"/>
-      <c r="R316" t="inlineStr"/>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S316" t="inlineStr"/>
       <c r="T316" t="inlineStr">
         <is>
@@ -29059,12 +29079,12 @@
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V316" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29096,12 +29116,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>C000232398</t>
+          <t>C000236724</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>C000232398 - BRAVO HUANACO ALEJANDRINA ALFONSA</t>
+          <t>C000236724 - LUQUE MAMANI EUGENIA</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -29132,12 +29152,12 @@
       <c r="O317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -29148,13 +29168,17 @@
       <c r="S317" t="inlineStr"/>
       <c r="T317" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U317" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29176,7 +29200,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -29186,12 +29210,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>C000232420</t>
+          <t>C001403722</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>C000232420 - SANTISTEBAN TEJADA MANUEL</t>
+          <t>C001403722 - SALLUCA JIMENEZ JORGE JESUS</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -29258,7 +29282,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -29268,17 +29292,17 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>C000232429</t>
+          <t>C001385811</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>C000232429 - TICONA MOYA ELISA</t>
+          <t>C001385811 - CRUZZATT FIGUEROA SALUTINIANO</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I319" s="2" t="n">
@@ -29291,7 +29315,7 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -29302,21 +29326,9 @@
       <c r="M319" t="inlineStr"/>
       <c r="N319" t="inlineStr"/>
       <c r="O319" t="inlineStr"/>
-      <c r="P319" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q319" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R319" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P319" t="inlineStr"/>
+      <c r="Q319" t="inlineStr"/>
+      <c r="R319" t="inlineStr"/>
       <c r="S319" t="inlineStr"/>
       <c r="T319" t="inlineStr">
         <is>
@@ -29325,12 +29337,12 @@
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V319" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -29362,12 +29374,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>C000232644</t>
+          <t>C001517901</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>C000232644 - CHARQUI CRUZ NORMA LOLA</t>
+          <t>C001517901 - AÑANCA QUISPE OSCAR</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -29403,7 +29415,7 @@
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -29446,7 +29458,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -29456,17 +29468,17 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>C000236724</t>
+          <t>C001465182</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>C000236724 - LUQUE MAMANI EUGENIA</t>
+          <t>C001465182 - LEFONCIO SANCHEZ CRISTIAN ALEXIS</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I321" s="2" t="n">
@@ -29479,7 +29491,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -29490,21 +29502,9 @@
       <c r="M321" t="inlineStr"/>
       <c r="N321" t="inlineStr"/>
       <c r="O321" t="inlineStr"/>
-      <c r="P321" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q321" t="inlineStr">
-        <is>
-          <t>Ver promociones</t>
-        </is>
-      </c>
-      <c r="R321" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P321" t="inlineStr"/>
+      <c r="Q321" t="inlineStr"/>
+      <c r="R321" t="inlineStr"/>
       <c r="S321" t="inlineStr"/>
       <c r="T321" t="inlineStr">
         <is>
@@ -29550,12 +29550,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>C004095661</t>
+          <t>C004167639</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>C004095661 - YOMONA INCIO MIRIAM ANA</t>
+          <t>C004167639 - K &amp; D STORE E.I.R.L.</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -29634,7 +29634,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cliente no usa / no quiere usar el código indicado</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -29644,17 +29644,17 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>C004043607</t>
+          <t>C004169201</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>C004043607 - FLORES LEON MARISELLA DEL CARMEN</t>
+          <t>C004169201 - URDIALES GUERRERO BRYAN JUNIOR</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I323" s="2" t="n">
@@ -29667,7 +29667,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -29678,35 +29678,19 @@
       <c r="M323" t="inlineStr"/>
       <c r="N323" t="inlineStr"/>
       <c r="O323" t="inlineStr"/>
-      <c r="P323" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q323" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R323" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P323" t="inlineStr"/>
+      <c r="Q323" t="inlineStr"/>
+      <c r="R323" t="inlineStr"/>
       <c r="S323" t="inlineStr"/>
       <c r="T323" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U323" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr"/>
       <c r="V323" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -29738,12 +29722,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>C004143038</t>
+          <t>C004043607</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>C004143038 - BAO MORALES ALFREDO ALEJANDRO</t>
+          <t>C004043607 - FLORES LEON MARISELLA DEL CARMEN</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -29832,12 +29816,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>C004167639</t>
+          <t>C004095661</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>C004167639 - K &amp; D STORE E.I.R.L.</t>
+          <t>C004095661 - YOMONA INCIO MIRIAM ANA</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -29916,7 +29900,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Cliente no usa / no quiere usar el código indicado</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -29926,17 +29910,17 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>C004169201</t>
+          <t>C004143038</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>C004169201 - URDIALES GUERRERO BRYAN JUNIOR</t>
+          <t>C004143038 - BAO MORALES ALFREDO ALEJANDRO</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I326" s="2" t="n">
@@ -29949,7 +29933,7 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -29960,19 +29944,35 @@
       <c r="M326" t="inlineStr"/>
       <c r="N326" t="inlineStr"/>
       <c r="O326" t="inlineStr"/>
-      <c r="P326" t="inlineStr"/>
-      <c r="Q326" t="inlineStr"/>
-      <c r="R326" t="inlineStr"/>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S326" t="inlineStr"/>
       <c r="T326" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U326" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V326" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -30004,17 +30004,17 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>C001562430</t>
+          <t>C001419064</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>C001562430 - CANO YARANGA MIRIAM NOHEMI</t>
+          <t>C001419064 - AZO CONTRERAS ANITA MARCELA</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I327" s="2" t="n">
@@ -30027,7 +30027,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -30038,21 +30038,9 @@
       <c r="M327" t="inlineStr"/>
       <c r="N327" t="inlineStr"/>
       <c r="O327" t="inlineStr"/>
-      <c r="P327" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>Confirmar pedido</t>
-        </is>
-      </c>
-      <c r="R327" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="inlineStr"/>
+      <c r="R327" t="inlineStr"/>
       <c r="S327" t="inlineStr"/>
       <c r="T327" t="inlineStr">
         <is>
@@ -30061,12 +30049,12 @@
       </c>
       <c r="U327" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V327" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -30098,12 +30086,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>C001544950</t>
+          <t>C001319535</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>C001544950 - VILA DE CAMACHO MARIA ELENA</t>
+          <t>C001319535 - PALOMINO CCOYLLULLI ZENOBIA</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -30139,7 +30127,7 @@
       </c>
       <c r="Q328" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -30192,12 +30180,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>C001462473</t>
+          <t>C001435529</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>C001462473 - JARAMILLO PEREZ SANDRA ISABEL</t>
+          <t>C001435529 - MARQUINA GUTIERREZ ERIKA PATRICIA</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -30233,7 +30221,7 @@
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -30286,12 +30274,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>C001319535</t>
+          <t>C001462473</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>C001319535 - PALOMINO CCOYLLULLI ZENOBIA</t>
+          <t>C001462473 - JARAMILLO PEREZ SANDRA ISABEL</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -30380,12 +30368,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>C001435529</t>
+          <t>C001562430</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>C001435529 - MARQUINA GUTIERREZ ERIKA PATRICIA</t>
+          <t>C001562430 - CANO YARANGA MIRIAM NOHEMI</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -30421,7 +30409,7 @@
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -30464,7 +30452,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -30474,17 +30462,17 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>C001419064</t>
+          <t>C001544950</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>C001419064 - AZO CONTRERAS ANITA MARCELA</t>
+          <t>C001544950 - VILA DE CAMACHO MARIA ELENA</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I332" s="2" t="n">
@@ -30497,7 +30485,7 @@
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -30508,9 +30496,21 @@
       <c r="M332" t="inlineStr"/>
       <c r="N332" t="inlineStr"/>
       <c r="O332" t="inlineStr"/>
-      <c r="P332" t="inlineStr"/>
-      <c r="Q332" t="inlineStr"/>
-      <c r="R332" t="inlineStr"/>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S332" t="inlineStr"/>
       <c r="T332" t="inlineStr">
         <is>
@@ -30519,12 +30519,12 @@
       </c>
       <c r="U332" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V332" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -31098,7 +31098,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -31108,17 +31108,17 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>C001389592</t>
+          <t>C001172117</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>C001389592 - JUAREZ CABEZAS VDA DE ALARCON BERTHA</t>
+          <t>C001172117 - TORRES SOLORZANO IGNACIA</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I339" s="2" t="n">
@@ -31131,7 +31131,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -31142,9 +31142,21 @@
       <c r="M339" t="inlineStr"/>
       <c r="N339" t="inlineStr"/>
       <c r="O339" t="inlineStr"/>
-      <c r="P339" t="inlineStr"/>
-      <c r="Q339" t="inlineStr"/>
-      <c r="R339" t="inlineStr"/>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S339" t="inlineStr"/>
       <c r="T339" t="inlineStr">
         <is>
@@ -31180,7 +31192,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -31190,17 +31202,17 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>C001395870</t>
+          <t>C001389592</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>C001395870 - ROJO ROJAS SAMANDA ROSAURA</t>
+          <t>C001389592 - JUAREZ CABEZAS VDA DE ALARCON BERTHA</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I340" s="2" t="n">
@@ -31213,7 +31225,7 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -31224,21 +31236,9 @@
       <c r="M340" t="inlineStr"/>
       <c r="N340" t="inlineStr"/>
       <c r="O340" t="inlineStr"/>
-      <c r="P340" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q340" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R340" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P340" t="inlineStr"/>
+      <c r="Q340" t="inlineStr"/>
+      <c r="R340" t="inlineStr"/>
       <c r="S340" t="inlineStr"/>
       <c r="T340" t="inlineStr">
         <is>
@@ -31284,12 +31284,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>C001172117</t>
+          <t>C001395870</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>C001172117 - TORRES SOLORZANO IGNACIA</t>
+          <t>C001395870 - ROJO ROJAS SAMANDA ROSAURA</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="Q341" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -31546,12 +31546,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>C001759336</t>
+          <t>C001752700</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>C001759336 - LUQUE LIPA LUCIANO ALFREDO</t>
+          <t>C001752700 - AYALA GAVILAN DE PEREZ ZOILA PAULINA</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -31591,12 +31591,12 @@
       </c>
       <c r="U344" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V344" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -31618,7 +31618,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -31628,17 +31628,17 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>C001736029</t>
+          <t>C001759336</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>C001736029 - GALLEGOS VALDERRAMA MARIA ISABEL</t>
+          <t>C001759336 - LUQUE LIPA LUCIANO ALFREDO</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I345" s="2" t="n">
@@ -31651,7 +31651,7 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -31662,21 +31662,9 @@
       <c r="M345" t="inlineStr"/>
       <c r="N345" t="inlineStr"/>
       <c r="O345" t="inlineStr"/>
-      <c r="P345" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q345" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R345" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P345" t="inlineStr"/>
+      <c r="Q345" t="inlineStr"/>
+      <c r="R345" t="inlineStr"/>
       <c r="S345" t="inlineStr"/>
       <c r="T345" t="inlineStr">
         <is>
@@ -31685,12 +31673,12 @@
       </c>
       <c r="U345" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V345" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -31722,12 +31710,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>C001748948</t>
+          <t>C001736029</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>C001748948 - MAURICIO AYALA GIOVANNA MARGARITA</t>
+          <t>C001736029 - GALLEGOS VALDERRAMA MARIA ISABEL</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -31774,13 +31762,17 @@
       <c r="S346" t="inlineStr"/>
       <c r="T346" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U346" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V346" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -31802,7 +31794,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -31812,17 +31804,17 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>C001752700</t>
+          <t>C001748948</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>C001752700 - AYALA GAVILAN DE PEREZ ZOILA PAULINA</t>
+          <t>C001748948 - MAURICIO AYALA GIOVANNA MARGARITA</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I347" s="2" t="n">
@@ -31835,7 +31827,7 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -31846,23 +31838,31 @@
       <c r="M347" t="inlineStr"/>
       <c r="N347" t="inlineStr"/>
       <c r="O347" t="inlineStr"/>
-      <c r="P347" t="inlineStr"/>
-      <c r="Q347" t="inlineStr"/>
-      <c r="R347" t="inlineStr"/>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S347" t="inlineStr"/>
       <c r="T347" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U347" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr"/>
       <c r="V347" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -31894,12 +31894,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>C001759891</t>
+          <t>C004043199</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>C001759891 - DIAZ VILLAFANE ERIK EUGENIO</t>
+          <t>C004043199 - VARGAS RODRIGUEZ TANIA PATRICIA</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -31946,13 +31946,17 @@
       <c r="S348" t="inlineStr"/>
       <c r="T348" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U348" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V348" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -31984,12 +31988,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>C001759896</t>
+          <t>C001759900</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>C001759896 - VILLAVERDE ARIAS EFRAIN JORGE</t>
+          <t>C001759900 - AGUILAR QUINONES GABRIEL ERNALDO</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -32078,12 +32082,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>C001759900</t>
+          <t>C001759896</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>C001759900 - AGUILAR QUINONES GABRIEL ERNALDO</t>
+          <t>C001759896 - VILLAVERDE ARIAS EFRAIN JORGE</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -32172,12 +32176,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>C004043199</t>
+          <t>C001759891</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>C004043199 - VARGAS RODRIGUEZ TANIA PATRICIA</t>
+          <t>C001759891 - DIAZ VILLAFANE ERIK EUGENIO</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -32224,17 +32228,13 @@
       <c r="S351" t="inlineStr"/>
       <c r="T351" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U351" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr"/>
       <c r="V351" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -32548,12 +32548,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>C001531786</t>
+          <t>C001389739</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>C001531786 - BRAVO GALLARDO GIOVANNA AZUCENA</t>
+          <t>C001389739 - YUPANQUI CANARES NORMA YOLANDA</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -32736,12 +32736,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>C001564298</t>
+          <t>C001531786</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>C001564298 - PINTO CONDORI MARIBEL</t>
+          <t>C001531786 - BRAVO GALLARDO GIOVANNA AZUCENA</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -32777,7 +32777,7 @@
       </c>
       <c r="Q357" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -32793,12 +32793,12 @@
       </c>
       <c r="U357" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V357" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -32830,12 +32830,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>C001389739</t>
+          <t>C001564298</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>C001389739 - YUPANQUI CANARES NORMA YOLANDA</t>
+          <t>C001564298 - PINTO CONDORI MARIBEL</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -32871,7 +32871,7 @@
       </c>
       <c r="Q358" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
@@ -32887,12 +32887,12 @@
       </c>
       <c r="U358" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V358" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -32914,7 +32914,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -32924,17 +32924,17 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>C004221118</t>
+          <t>C001345219</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>C004221118 - SUAREZ ROAS KATHERINE JAZMIN</t>
+          <t>C001345219 - MARQUEZ SUCA EDGAR LEONIDAS</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I359" s="2" t="n">
@@ -32947,7 +32947,7 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -32958,21 +32958,9 @@
       <c r="M359" t="inlineStr"/>
       <c r="N359" t="inlineStr"/>
       <c r="O359" t="inlineStr"/>
-      <c r="P359" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q359" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="R359" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P359" t="inlineStr"/>
+      <c r="Q359" t="inlineStr"/>
+      <c r="R359" t="inlineStr"/>
       <c r="S359" t="inlineStr"/>
       <c r="T359" t="inlineStr">
         <is>
@@ -33018,12 +33006,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>C000233799</t>
+          <t>C001174025</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>C000233799 - DELGADO DELGADO DE VELASQUEZ ANA MARIA</t>
+          <t>C001174025 - JARA MOGOLLON YOWEL SABINO</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -33059,7 +33047,7 @@
       </c>
       <c r="Q360" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
@@ -33112,12 +33100,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>C001638213</t>
+          <t>C000233799</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>C001638213 - GAVILAN ZAMORA DE HUAMAN IRIS CLOTILDE</t>
+          <t>C000233799 - DELGADO DELGADO DE VELASQUEZ ANA MARIA</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -33153,7 +33141,7 @@
       </c>
       <c r="Q361" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
@@ -33164,13 +33152,17 @@
       <c r="S361" t="inlineStr"/>
       <c r="T361" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U361" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V361" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -33202,12 +33194,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>C001411066</t>
+          <t>C001388969</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>C001411066 - SOLORZANO DE LA CRUZ ODELI ELIZABETH</t>
+          <t>C001388969 - BERROCAL PORRAS BEATRIZ</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -33284,12 +33276,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>C001759255</t>
+          <t>C001332729</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>C001759255 - VILCA QUISPE DE LEQUERNAQUE MARIA ISABEL</t>
+          <t>C001332729 - PALOMINO QUISPE CHRIS JANNET</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -33325,7 +33317,7 @@
       </c>
       <c r="Q363" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
@@ -33336,13 +33328,17 @@
       <c r="S363" t="inlineStr"/>
       <c r="T363" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U363" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V363" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -33364,7 +33360,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -33374,17 +33370,17 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>C004183906</t>
+          <t>C001326427</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>C004183906 - SANABRE PARI NORMA</t>
+          <t>C001326427 - VARGAS PAREDES CELIA</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I364" s="2" t="n">
@@ -33397,7 +33393,7 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -33408,9 +33404,21 @@
       <c r="M364" t="inlineStr"/>
       <c r="N364" t="inlineStr"/>
       <c r="O364" t="inlineStr"/>
-      <c r="P364" t="inlineStr"/>
-      <c r="Q364" t="inlineStr"/>
-      <c r="R364" t="inlineStr"/>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S364" t="inlineStr"/>
       <c r="T364" t="inlineStr">
         <is>
@@ -33419,12 +33427,12 @@
       </c>
       <c r="U364" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V364" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -33456,12 +33464,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>C004184357</t>
+          <t>C001555857</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>C004184357 - CRESPIN ROSALES CLARA</t>
+          <t>C001555857 - WONG ESPINOZA AURELIO MANUEL</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -33487,11 +33495,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M365" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M365" t="inlineStr"/>
       <c r="N365" t="inlineStr"/>
       <c r="O365" t="inlineStr"/>
       <c r="P365" t="inlineStr">
@@ -33554,12 +33558,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>C004183897</t>
+          <t>C004221118</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>C004183897 - ACHAHUANCO DIAZ EFRAIN</t>
+          <t>C004221118 - SUAREZ ROAS KATHERINE JAZMIN</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -33638,7 +33642,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -33648,17 +33652,17 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>C004181409</t>
+          <t>C004183906</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>C004181409 - MISIYAURI TITO RIGOBERTO URBANO</t>
+          <t>C004183906 - SANABRE PARI NORMA</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I367" s="2" t="n">
@@ -33671,7 +33675,7 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -33682,21 +33686,9 @@
       <c r="M367" t="inlineStr"/>
       <c r="N367" t="inlineStr"/>
       <c r="O367" t="inlineStr"/>
-      <c r="P367" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q367" t="inlineStr">
-        <is>
-          <t>Confirmar pedido</t>
-        </is>
-      </c>
-      <c r="R367" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P367" t="inlineStr"/>
+      <c r="Q367" t="inlineStr"/>
+      <c r="R367" t="inlineStr"/>
       <c r="S367" t="inlineStr"/>
       <c r="T367" t="inlineStr">
         <is>
@@ -33705,12 +33697,12 @@
       </c>
       <c r="U367" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V367" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -33742,12 +33734,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>C004212545</t>
+          <t>C004184357</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>C004212545 - GELDRES VENTOCILLA MARTHA YAKELINE</t>
+          <t>C004184357 - CRESPIN ROSALES CLARA</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -33773,7 +33765,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M368" t="inlineStr"/>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N368" t="inlineStr"/>
       <c r="O368" t="inlineStr"/>
       <c r="P368" t="inlineStr">
@@ -33783,7 +33779,7 @@
       </c>
       <c r="Q368" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
@@ -33826,7 +33822,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -33836,17 +33832,17 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>C004163503</t>
+          <t>C001638213</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>C004163503 - QUISPE INCA ISABEL</t>
+          <t>C001638213 - GAVILAN ZAMORA DE HUAMAN IRIS CLOTILDE</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I369" s="2" t="n">
@@ -33859,7 +33855,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -33870,23 +33866,31 @@
       <c r="M369" t="inlineStr"/>
       <c r="N369" t="inlineStr"/>
       <c r="O369" t="inlineStr"/>
-      <c r="P369" t="inlineStr"/>
-      <c r="Q369" t="inlineStr"/>
-      <c r="R369" t="inlineStr"/>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S369" t="inlineStr"/>
       <c r="T369" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U369" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr"/>
       <c r="V369" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -33908,7 +33912,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No tiene tiempo para capacitarse</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -33918,17 +33922,17 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>C001555857</t>
+          <t>C001411066</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>C001555857 - WONG ESPINOZA AURELIO MANUEL</t>
+          <t>C001411066 - SOLORZANO DE LA CRUZ ODELI ELIZABETH</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I370" s="2" t="n">
@@ -33941,7 +33945,7 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -33952,21 +33956,9 @@
       <c r="M370" t="inlineStr"/>
       <c r="N370" t="inlineStr"/>
       <c r="O370" t="inlineStr"/>
-      <c r="P370" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q370" t="inlineStr">
-        <is>
-          <t>Confirmar pedido</t>
-        </is>
-      </c>
-      <c r="R370" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P370" t="inlineStr"/>
+      <c r="Q370" t="inlineStr"/>
+      <c r="R370" t="inlineStr"/>
       <c r="S370" t="inlineStr"/>
       <c r="T370" t="inlineStr">
         <is>
@@ -34012,12 +34004,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>C001742707</t>
+          <t>C001759255</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>C001742707 - QUISPE COLLANTE MARCELINA</t>
+          <t>C001759255 - VILCA QUISPE DE LEQUERNAQUE MARIA ISABEL</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -34053,7 +34045,7 @@
       </c>
       <c r="Q371" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="R371" t="inlineStr">
@@ -34064,17 +34056,13 @@
       <c r="S371" t="inlineStr"/>
       <c r="T371" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U371" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr"/>
       <c r="V371" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -34106,12 +34094,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>C001681427</t>
+          <t>C004183897</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>C001681427 - MIO MENDOZA MARITZA</t>
+          <t>C004183897 - ACHAHUANCO DIAZ EFRAIN</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -34147,7 +34135,7 @@
       </c>
       <c r="Q372" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="R372" t="inlineStr">
@@ -34158,13 +34146,17 @@
       <c r="S372" t="inlineStr"/>
       <c r="T372" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U372" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V372" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -34186,7 +34178,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -34196,17 +34188,17 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>C001388969</t>
+          <t>C004181409</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>C001388969 - BERROCAL PORRAS BEATRIZ</t>
+          <t>C004181409 - MISIYAURI TITO RIGOBERTO URBANO</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I373" s="2" t="n">
@@ -34219,7 +34211,7 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -34230,9 +34222,21 @@
       <c r="M373" t="inlineStr"/>
       <c r="N373" t="inlineStr"/>
       <c r="O373" t="inlineStr"/>
-      <c r="P373" t="inlineStr"/>
-      <c r="Q373" t="inlineStr"/>
-      <c r="R373" t="inlineStr"/>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S373" t="inlineStr"/>
       <c r="T373" t="inlineStr">
         <is>
@@ -34268,7 +34272,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>No tiene tiempo para capacitarse</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -34278,12 +34282,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>C001345219</t>
+          <t>C004163503</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>C001345219 - MARQUEZ SUCA EDGAR LEONIDAS</t>
+          <t>C004163503 - QUISPE INCA ISABEL</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -34360,12 +34364,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>C001326427</t>
+          <t>C004212545</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>C001326427 - VARGAS PAREDES CELIA</t>
+          <t>C004212545 - GELDRES VENTOCILLA MARTHA YAKELINE</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -34454,12 +34458,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>C001174025</t>
+          <t>C001681427</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>C001174025 - JARA MOGOLLON YOWEL SABINO</t>
+          <t>C001681427 - MIO MENDOZA MARITZA</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -34506,17 +34510,13 @@
       <c r="S376" t="inlineStr"/>
       <c r="T376" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U376" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr"/>
       <c r="V376" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -34548,12 +34548,12 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>C001332729</t>
+          <t>C001742707</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>C001332729 - PALOMINO QUISPE CHRIS JANNET</t>
+          <t>C001742707 - QUISPE COLLANTE MARCELINA</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -34589,7 +34589,7 @@
       </c>
       <c r="Q377" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="R377" t="inlineStr">
